--- a/new_sales_order_sheet_format 1 - Copy-1 (6).xlsx
+++ b/new_sales_order_sheet_format 1 - Copy-1 (6).xlsx
@@ -336,7 +336,7 @@
     <t>Apr.20,2026</t>
   </si>
   <si>
-    <t>15E09A7001</t>
+    <t>15E09A8009</t>
   </si>
   <si>
     <t>Dec.12,2025</t>
@@ -345,28 +345,28 @@
     <t>AW2026</t>
   </si>
   <si>
-    <t>15F09A7001</t>
-  </si>
-  <si>
-    <t>15G09A7001</t>
-  </si>
-  <si>
-    <t>15H09A7001</t>
-  </si>
-  <si>
-    <t>15I09A7001</t>
-  </si>
-  <si>
-    <t>15J09A7001</t>
-  </si>
-  <si>
-    <t>15K09A7001</t>
-  </si>
-  <si>
-    <t>15L09A7001</t>
-  </si>
-  <si>
-    <t>15M09A7001</t>
+    <t>15F09A8009</t>
+  </si>
+  <si>
+    <t>15G09A8009</t>
+  </si>
+  <si>
+    <t>15H09A8009</t>
+  </si>
+  <si>
+    <t>15I09A8009</t>
+  </si>
+  <si>
+    <t>15J09A8009</t>
+  </si>
+  <si>
+    <t>15K09A8009</t>
+  </si>
+  <si>
+    <t>15L09A8009</t>
+  </si>
+  <si>
+    <t>15M09A8009</t>
   </si>
   <si>
     <t>Olny Excel formate Change</t>

--- a/new_sales_order_sheet_format 1 - Copy-1 (6).xlsx
+++ b/new_sales_order_sheet_format 1 - Copy-1 (6).xlsx
@@ -336,7 +336,7 @@
     <t>Apr.20,2026</t>
   </si>
   <si>
-    <t>15E09A8009</t>
+    <t>15E09A9042</t>
   </si>
   <si>
     <t>Dec.12,2025</t>
@@ -345,28 +345,28 @@
     <t>AW2026</t>
   </si>
   <si>
-    <t>15F09A8009</t>
-  </si>
-  <si>
-    <t>15G09A8009</t>
-  </si>
-  <si>
-    <t>15H09A8009</t>
-  </si>
-  <si>
-    <t>15I09A8009</t>
-  </si>
-  <si>
-    <t>15J09A8009</t>
-  </si>
-  <si>
-    <t>15K09A8009</t>
-  </si>
-  <si>
-    <t>15L09A8009</t>
-  </si>
-  <si>
-    <t>15M09A8009</t>
+    <t>15F09A9042</t>
+  </si>
+  <si>
+    <t>15G09A9042</t>
+  </si>
+  <si>
+    <t>15H09A9042</t>
+  </si>
+  <si>
+    <t>15I09A9042</t>
+  </si>
+  <si>
+    <t>15J09A9042</t>
+  </si>
+  <si>
+    <t>15K09A9042</t>
+  </si>
+  <si>
+    <t>15L09A9042</t>
+  </si>
+  <si>
+    <t>15M09A9042</t>
   </si>
   <si>
     <t>Olny Excel formate Change</t>
@@ -409,17 +409,10 @@
     <numFmt numFmtId="166" formatCode="[$-409]d/mmm/yy;@"/>
     <numFmt numFmtId="167" formatCode="[$-409]dd/mmm/yy;@"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
-      <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <charset val="134"/>
-      <color theme="1"/>
       <scheme val="minor"/>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -503,98 +496,98 @@
   </cellStyleXfs>
   <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="15" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="15" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="15" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -903,7 +896,7 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:AC269"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="17.85546875"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="17.85546875"/>
   <cols>
     <col min="1" max="18" width="17.85546875" style="1" customWidth="1"/>
     <col min="19" max="19" width="17.85546875" style="2" customWidth="1"/>
@@ -4867,7 +4860,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9.140625"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="9.140625"/>
   <cols>
     <col min="1" max="1" width="20.140625" customWidth="1"/>
     <col min="2" max="2" width="20.42578125" customWidth="1"/>
@@ -4942,7 +4935,7 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:AF269"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="17.85546875"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="17.85546875"/>
   <cols>
     <col min="1" max="2" width="17.85546875" style="1" customWidth="1"/>
     <col min="3" max="3" width="14" style="1" customWidth="1"/>

--- a/new_sales_order_sheet_format 1 - Copy-1 (6).xlsx
+++ b/new_sales_order_sheet_format 1 - Copy-1 (6).xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30527"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3D5550A-3746-4C47-ABC0-FED4CB205596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="15720" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Previous" sheetId="1" r:id="rId1"/>
-    <sheet name="Need Update" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet2" sheetId="3" r:id="rId3"/>
+    <sheet sheetId="1" name="Previous" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Need Update" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Sheet2" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -322,7 +321,7 @@
     <t>CAT784-1A23S</t>
   </si>
   <si>
-    <t>15E09A9125</t>
+    <t>15E09A9153</t>
   </si>
   <si>
     <t>Dec.12,2025</t>
@@ -331,43 +330,43 @@
     <t>AW2026</t>
   </si>
   <si>
-    <t>CAT344-1A23W</t>
+    <t>CAT000-1A029</t>
   </si>
   <si>
-    <t>15F09A9125</t>
+    <t>15F09A9153</t>
   </si>
   <si>
     <t>CAT960-1A23S</t>
   </si>
   <si>
-    <t>15G09A9125</t>
+    <t>15G09A9153</t>
   </si>
   <si>
-    <t>15H09A9125</t>
+    <t>15H09A9153</t>
   </si>
   <si>
-    <t>15I09A9125</t>
+    <t>15I09A9153</t>
   </si>
   <si>
     <t>CAT888-1A23S</t>
   </si>
   <si>
-    <t>15J09A9125</t>
+    <t>15J09A9153</t>
   </si>
   <si>
     <t>CAT1100-1A23W</t>
   </si>
   <si>
-    <t>15K09A9125</t>
+    <t>15K09A9153</t>
   </si>
   <si>
     <t>CAT1100-3A23W</t>
   </si>
   <si>
-    <t>15L09A9125</t>
+    <t>15L09A9153</t>
   </si>
   <si>
-    <t>15M09A9125</t>
+    <t>15M09A9153</t>
   </si>
   <si>
     <t>Olny Excel formate Change</t>
@@ -406,57 +405,57 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <family val="2"/>
       <sz val="12"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
+      <family val="1"/>
       <sz val="9"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
       <b/>
+      <family val="1"/>
       <sz val="9"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
+      <family val="2"/>
       <sz val="9"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
+      <color rgb="FFFF0000"/>
+      <family val="1"/>
       <sz val="9"/>
-      <color rgb="FFFF0000"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
       <b/>
+      <color rgb="FFFF0000"/>
+      <family val="1"/>
       <sz val="9"/>
-      <color rgb="FFFF0000"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
+      <family val="2"/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -535,15 +534,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -885,14 +884,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AC269"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="29" width="17.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="15.75" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -957,7 +956,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" ht="21" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>21</v>
       </c>
@@ -1026,7 +1025,7 @@
       <c r="AB2" s="10"/>
       <c r="AC2" s="10"/>
     </row>
-    <row r="3" spans="1:29" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="21" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>21</v>
       </c>
@@ -1095,7 +1094,7 @@
       <c r="AB3" s="10"/>
       <c r="AC3" s="10"/>
     </row>
-    <row r="4" spans="1:29" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="21" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>21</v>
       </c>
@@ -1164,7 +1163,7 @@
       <c r="AB4" s="10"/>
       <c r="AC4" s="10"/>
     </row>
-    <row r="5" spans="1:29" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="21" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>21</v>
       </c>
@@ -1233,7 +1232,7 @@
       <c r="AB5" s="10"/>
       <c r="AC5" s="10"/>
     </row>
-    <row r="6" spans="1:29" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="21" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>21</v>
       </c>
@@ -1302,7 +1301,7 @@
       <c r="AB6" s="10"/>
       <c r="AC6" s="10"/>
     </row>
-    <row r="7" spans="1:29" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="21" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>21</v>
       </c>
@@ -1371,7 +1370,7 @@
       <c r="AB7" s="10"/>
       <c r="AC7" s="10"/>
     </row>
-    <row r="8" spans="1:29" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="21" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>21</v>
       </c>
@@ -1440,7 +1439,7 @@
       <c r="AB8" s="10"/>
       <c r="AC8" s="10"/>
     </row>
-    <row r="9" spans="1:29" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="21" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>21</v>
       </c>
@@ -1509,7 +1508,7 @@
       <c r="AB9" s="10"/>
       <c r="AC9" s="10"/>
     </row>
-    <row r="10" spans="1:29" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" ht="21" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>21</v>
       </c>
@@ -1578,7 +1577,7 @@
       <c r="AB10" s="10"/>
       <c r="AC10" s="10"/>
     </row>
-    <row r="11" spans="1:29" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" ht="21" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -1609,7 +1608,7 @@
       <c r="AB11" s="10"/>
       <c r="AC11" s="10"/>
     </row>
-    <row r="12" spans="1:29" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" ht="21" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -1640,7 +1639,7 @@
       <c r="AB12" s="10"/>
       <c r="AC12" s="10"/>
     </row>
-    <row r="13" spans="1:29" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" ht="21" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -1671,7 +1670,7 @@
       <c r="AB13" s="10"/>
       <c r="AC13" s="10"/>
     </row>
-    <row r="14" spans="1:29" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" ht="21" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
@@ -1702,7 +1701,7 @@
       <c r="AB14" s="10"/>
       <c r="AC14" s="10"/>
     </row>
-    <row r="15" spans="1:29" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" ht="21" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" s="4"/>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -1733,7 +1732,7 @@
       <c r="AB15" s="10"/>
       <c r="AC15" s="10"/>
     </row>
-    <row r="16" spans="1:29" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" ht="21" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" s="4"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
@@ -1764,7 +1763,7 @@
       <c r="AB16" s="10"/>
       <c r="AC16" s="10"/>
     </row>
-    <row r="17" spans="1:29" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" ht="21" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" s="4"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
@@ -1795,7 +1794,7 @@
       <c r="AB17" s="10"/>
       <c r="AC17" s="10"/>
     </row>
-    <row r="18" spans="1:29" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" ht="21" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" s="4"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
@@ -1826,7 +1825,7 @@
       <c r="AB18" s="10"/>
       <c r="AC18" s="10"/>
     </row>
-    <row r="19" spans="1:29" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" ht="21" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" s="4"/>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
@@ -1857,7 +1856,7 @@
       <c r="AB19" s="10"/>
       <c r="AC19" s="10"/>
     </row>
-    <row r="20" spans="1:29" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" ht="21" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="4"/>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
@@ -1888,7 +1887,7 @@
       <c r="AB20" s="10"/>
       <c r="AC20" s="10"/>
     </row>
-    <row r="21" spans="1:29" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" ht="21" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" s="4"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
@@ -1919,7 +1918,7 @@
       <c r="AB21" s="10"/>
       <c r="AC21" s="10"/>
     </row>
-    <row r="22" spans="1:29" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" ht="21" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A22" s="4"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -1950,7 +1949,7 @@
       <c r="AB22" s="10"/>
       <c r="AC22" s="10"/>
     </row>
-    <row r="23" spans="1:29" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" ht="21" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -1981,7 +1980,7 @@
       <c r="AB23" s="10"/>
       <c r="AC23" s="10"/>
     </row>
-    <row r="24" spans="1:29" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" ht="21" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A24" s="4"/>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
@@ -2012,7 +2011,7 @@
       <c r="AB24" s="10"/>
       <c r="AC24" s="10"/>
     </row>
-    <row r="25" spans="1:29" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" ht="21" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="12"/>
       <c r="B25" s="12"/>
       <c r="C25" s="4"/>
@@ -2035,7 +2034,7 @@
       <c r="T25" s="8"/>
       <c r="U25" s="13"/>
     </row>
-    <row r="26" spans="1:29" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" ht="21" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="12"/>
       <c r="B26" s="12"/>
       <c r="C26" s="4"/>
@@ -2058,7 +2057,7 @@
       <c r="T26" s="8"/>
       <c r="U26" s="14"/>
     </row>
-    <row r="27" spans="1:29" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27" s="12"/>
       <c r="B27" s="12"/>
       <c r="C27" s="4"/>
@@ -2080,7 +2079,7 @@
       <c r="S27" s="8"/>
       <c r="T27" s="8"/>
     </row>
-    <row r="28" spans="1:29" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28" s="12"/>
       <c r="B28" s="12"/>
       <c r="C28" s="4"/>
@@ -2102,7 +2101,7 @@
       <c r="S28" s="8"/>
       <c r="T28" s="8"/>
     </row>
-    <row r="29" spans="1:29" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29" s="12"/>
       <c r="B29" s="12"/>
       <c r="C29" s="4"/>
@@ -2124,7 +2123,7 @@
       <c r="S29" s="8"/>
       <c r="T29" s="8"/>
     </row>
-    <row r="30" spans="1:29" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30" s="12"/>
       <c r="B30" s="12"/>
       <c r="C30" s="4"/>
@@ -2146,7 +2145,7 @@
       <c r="S30" s="8"/>
       <c r="T30" s="8"/>
     </row>
-    <row r="31" spans="1:29" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" ht="21" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="12"/>
       <c r="B31" s="12"/>
       <c r="C31" s="4"/>
@@ -2169,7 +2168,7 @@
       <c r="T31" s="8"/>
       <c r="U31" s="13"/>
     </row>
-    <row r="32" spans="1:29" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" ht="21" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="12"/>
       <c r="B32" s="12"/>
       <c r="C32" s="4"/>
@@ -2192,7 +2191,7 @@
       <c r="T32" s="8"/>
       <c r="U32" s="13"/>
     </row>
-    <row r="33" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" ht="21" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="12"/>
       <c r="B33" s="12"/>
       <c r="C33" s="4"/>
@@ -2215,7 +2214,7 @@
       <c r="T33" s="8"/>
       <c r="U33" s="13"/>
     </row>
-    <row r="34" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" ht="21" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="12"/>
       <c r="B34" s="12"/>
       <c r="C34" s="4"/>
@@ -2238,7 +2237,7 @@
       <c r="T34" s="8"/>
       <c r="U34" s="13"/>
     </row>
-    <row r="35" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A35" s="12"/>
       <c r="B35" s="12"/>
       <c r="C35" s="4"/>
@@ -2260,7 +2259,7 @@
       <c r="S35" s="8"/>
       <c r="T35" s="8"/>
     </row>
-    <row r="36" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" ht="21" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="12"/>
       <c r="B36" s="12"/>
       <c r="C36" s="4"/>
@@ -2283,7 +2282,7 @@
       <c r="T36" s="8"/>
       <c r="U36" s="14"/>
     </row>
-    <row r="37" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A37" s="12"/>
       <c r="B37" s="12"/>
       <c r="C37" s="4"/>
@@ -2305,7 +2304,7 @@
       <c r="S37" s="8"/>
       <c r="T37" s="8"/>
     </row>
-    <row r="38" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A38" s="12"/>
       <c r="B38" s="12"/>
       <c r="C38" s="4"/>
@@ -2327,7 +2326,7 @@
       <c r="S38" s="8"/>
       <c r="T38" s="8"/>
     </row>
-    <row r="39" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" ht="21" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="12"/>
       <c r="B39" s="12"/>
       <c r="C39" s="4"/>
@@ -2350,7 +2349,7 @@
       <c r="T39" s="8"/>
       <c r="U39" s="13"/>
     </row>
-    <row r="40" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" ht="21" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="12"/>
       <c r="B40" s="12"/>
       <c r="C40" s="4"/>
@@ -2373,7 +2372,7 @@
       <c r="T40" s="8"/>
       <c r="U40" s="13"/>
     </row>
-    <row r="41" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A41" s="12"/>
       <c r="B41" s="12"/>
       <c r="C41" s="4"/>
@@ -2395,7 +2394,7 @@
       <c r="S41" s="8"/>
       <c r="T41" s="8"/>
     </row>
-    <row r="42" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A42" s="12"/>
       <c r="B42" s="12"/>
       <c r="C42" s="4"/>
@@ -2417,7 +2416,7 @@
       <c r="S42" s="8"/>
       <c r="T42" s="8"/>
     </row>
-    <row r="43" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" ht="21" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="12"/>
       <c r="B43" s="12"/>
       <c r="C43" s="4"/>
@@ -2440,7 +2439,7 @@
       <c r="T43" s="8"/>
       <c r="U43" s="14"/>
     </row>
-    <row r="44" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A44" s="12"/>
       <c r="B44" s="12"/>
       <c r="C44" s="4"/>
@@ -2462,7 +2461,7 @@
       <c r="S44" s="8"/>
       <c r="T44" s="8"/>
     </row>
-    <row r="45" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" ht="21" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="12"/>
       <c r="B45" s="12"/>
       <c r="C45" s="4"/>
@@ -2485,7 +2484,7 @@
       <c r="T45" s="8"/>
       <c r="U45" s="14"/>
     </row>
-    <row r="46" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A46" s="12"/>
       <c r="B46" s="12"/>
       <c r="C46" s="4"/>
@@ -2507,7 +2506,7 @@
       <c r="S46" s="8"/>
       <c r="T46" s="8"/>
     </row>
-    <row r="47" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A47" s="12"/>
       <c r="B47" s="12"/>
       <c r="C47" s="4"/>
@@ -2529,7 +2528,7 @@
       <c r="S47" s="8"/>
       <c r="T47" s="8"/>
     </row>
-    <row r="48" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A48" s="12"/>
       <c r="B48" s="12"/>
       <c r="C48" s="4"/>
@@ -2551,7 +2550,7 @@
       <c r="S48" s="8"/>
       <c r="T48" s="8"/>
     </row>
-    <row r="49" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A49" s="12"/>
       <c r="B49" s="12"/>
       <c r="C49" s="4"/>
@@ -2573,7 +2572,7 @@
       <c r="S49" s="8"/>
       <c r="T49" s="8"/>
     </row>
-    <row r="50" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A50" s="12"/>
       <c r="B50" s="12"/>
       <c r="C50" s="4"/>
@@ -2595,7 +2594,7 @@
       <c r="S50" s="8"/>
       <c r="T50" s="8"/>
     </row>
-    <row r="51" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A51" s="12"/>
       <c r="B51" s="12"/>
       <c r="C51" s="4"/>
@@ -2617,7 +2616,7 @@
       <c r="S51" s="8"/>
       <c r="T51" s="8"/>
     </row>
-    <row r="52" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A52" s="12"/>
       <c r="B52" s="12"/>
       <c r="C52" s="4"/>
@@ -2639,7 +2638,7 @@
       <c r="S52" s="8"/>
       <c r="T52" s="8"/>
     </row>
-    <row r="53" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A53" s="12"/>
       <c r="B53" s="12"/>
       <c r="C53" s="4"/>
@@ -2661,7 +2660,7 @@
       <c r="S53" s="8"/>
       <c r="T53" s="8"/>
     </row>
-    <row r="54" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A54" s="12"/>
       <c r="B54" s="12"/>
       <c r="C54" s="4"/>
@@ -2683,7 +2682,7 @@
       <c r="S54" s="8"/>
       <c r="T54" s="8"/>
     </row>
-    <row r="55" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A55" s="12"/>
       <c r="B55" s="12"/>
       <c r="C55" s="4"/>
@@ -2705,7 +2704,7 @@
       <c r="S55" s="8"/>
       <c r="T55" s="8"/>
     </row>
-    <row r="56" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A56" s="12"/>
       <c r="B56" s="12"/>
       <c r="C56" s="4"/>
@@ -2727,7 +2726,7 @@
       <c r="S56" s="8"/>
       <c r="T56" s="8"/>
     </row>
-    <row r="57" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A57" s="12"/>
       <c r="B57" s="12"/>
       <c r="C57" s="4"/>
@@ -2749,7 +2748,7 @@
       <c r="S57" s="8"/>
       <c r="T57" s="8"/>
     </row>
-    <row r="58" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A58" s="12"/>
       <c r="B58" s="12"/>
       <c r="C58" s="4"/>
@@ -2771,7 +2770,7 @@
       <c r="S58" s="8"/>
       <c r="T58" s="8"/>
     </row>
-    <row r="59" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A59" s="12"/>
       <c r="B59" s="12"/>
       <c r="C59" s="4"/>
@@ -2793,7 +2792,7 @@
       <c r="S59" s="8"/>
       <c r="T59" s="8"/>
     </row>
-    <row r="60" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A60" s="12"/>
       <c r="B60" s="12"/>
       <c r="C60" s="4"/>
@@ -2815,7 +2814,7 @@
       <c r="S60" s="8"/>
       <c r="T60" s="8"/>
     </row>
-    <row r="61" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A61" s="12"/>
       <c r="B61" s="12"/>
       <c r="C61" s="4"/>
@@ -2837,7 +2836,7 @@
       <c r="S61" s="8"/>
       <c r="T61" s="8"/>
     </row>
-    <row r="62" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A62" s="12"/>
       <c r="B62" s="12"/>
       <c r="C62" s="4"/>
@@ -2859,7 +2858,7 @@
       <c r="S62" s="8"/>
       <c r="T62" s="8"/>
     </row>
-    <row r="63" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A63" s="12"/>
       <c r="B63" s="12"/>
       <c r="C63" s="4"/>
@@ -2881,7 +2880,7 @@
       <c r="S63" s="8"/>
       <c r="T63" s="8"/>
     </row>
-    <row r="64" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A64" s="12"/>
       <c r="B64" s="12"/>
       <c r="C64" s="4"/>
@@ -2903,7 +2902,7 @@
       <c r="S64" s="8"/>
       <c r="T64" s="8"/>
     </row>
-    <row r="65" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A65" s="12"/>
       <c r="B65" s="12"/>
       <c r="C65" s="4"/>
@@ -2925,7 +2924,7 @@
       <c r="S65" s="8"/>
       <c r="T65" s="8"/>
     </row>
-    <row r="66" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A66" s="12"/>
       <c r="B66" s="12"/>
       <c r="C66" s="4"/>
@@ -2947,7 +2946,7 @@
       <c r="S66" s="8"/>
       <c r="T66" s="8"/>
     </row>
-    <row r="67" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A67" s="12"/>
       <c r="B67" s="12"/>
       <c r="C67" s="4"/>
@@ -2969,7 +2968,7 @@
       <c r="S67" s="8"/>
       <c r="T67" s="8"/>
     </row>
-    <row r="68" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A68" s="12"/>
       <c r="B68" s="12"/>
       <c r="C68" s="4"/>
@@ -2991,7 +2990,7 @@
       <c r="S68" s="8"/>
       <c r="T68" s="8"/>
     </row>
-    <row r="69" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A69" s="12"/>
       <c r="B69" s="12"/>
       <c r="C69" s="4"/>
@@ -3013,7 +3012,7 @@
       <c r="S69" s="8"/>
       <c r="T69" s="8"/>
     </row>
-    <row r="70" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A70" s="12"/>
       <c r="B70" s="12"/>
       <c r="C70" s="4"/>
@@ -3035,7 +3034,7 @@
       <c r="S70" s="8"/>
       <c r="T70" s="8"/>
     </row>
-    <row r="71" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A71" s="12"/>
       <c r="B71" s="12"/>
       <c r="C71" s="4"/>
@@ -3057,7 +3056,7 @@
       <c r="S71" s="8"/>
       <c r="T71" s="8"/>
     </row>
-    <row r="72" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A72" s="12"/>
       <c r="B72" s="12"/>
       <c r="C72" s="4"/>
@@ -3079,7 +3078,7 @@
       <c r="S72" s="8"/>
       <c r="T72" s="8"/>
     </row>
-    <row r="73" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A73" s="12"/>
       <c r="B73" s="12"/>
       <c r="C73" s="4"/>
@@ -3101,7 +3100,7 @@
       <c r="S73" s="8"/>
       <c r="T73" s="8"/>
     </row>
-    <row r="74" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A74" s="12"/>
       <c r="B74" s="12"/>
       <c r="C74" s="4"/>
@@ -3123,7 +3122,7 @@
       <c r="S74" s="8"/>
       <c r="T74" s="8"/>
     </row>
-    <row r="75" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A75" s="12"/>
       <c r="B75" s="12"/>
       <c r="C75" s="4"/>
@@ -3145,7 +3144,7 @@
       <c r="S75" s="8"/>
       <c r="T75" s="8"/>
     </row>
-    <row r="76" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A76" s="12"/>
       <c r="B76" s="12"/>
       <c r="C76" s="4"/>
@@ -3167,7 +3166,7 @@
       <c r="S76" s="8"/>
       <c r="T76" s="8"/>
     </row>
-    <row r="77" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A77" s="12"/>
       <c r="B77" s="12"/>
       <c r="C77" s="4"/>
@@ -3189,7 +3188,7 @@
       <c r="S77" s="8"/>
       <c r="T77" s="8"/>
     </row>
-    <row r="78" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A78" s="12"/>
       <c r="B78" s="12"/>
       <c r="C78" s="4"/>
@@ -3211,7 +3210,7 @@
       <c r="S78" s="8"/>
       <c r="T78" s="8"/>
     </row>
-    <row r="79" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A79" s="12"/>
       <c r="B79" s="12"/>
       <c r="C79" s="4"/>
@@ -3233,7 +3232,7 @@
       <c r="S79" s="8"/>
       <c r="T79" s="8"/>
     </row>
-    <row r="80" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A80" s="12"/>
       <c r="B80" s="12"/>
       <c r="C80" s="4"/>
@@ -3255,7 +3254,7 @@
       <c r="S80" s="8"/>
       <c r="T80" s="8"/>
     </row>
-    <row r="81" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A81" s="12"/>
       <c r="B81" s="12"/>
       <c r="C81" s="4"/>
@@ -3277,7 +3276,7 @@
       <c r="S81" s="8"/>
       <c r="T81" s="8"/>
     </row>
-    <row r="82" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A82" s="12"/>
       <c r="B82" s="12"/>
       <c r="C82" s="4"/>
@@ -3299,7 +3298,7 @@
       <c r="S82" s="8"/>
       <c r="T82" s="8"/>
     </row>
-    <row r="83" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A83" s="12"/>
       <c r="B83" s="12"/>
       <c r="C83" s="4"/>
@@ -3321,7 +3320,7 @@
       <c r="S83" s="8"/>
       <c r="T83" s="8"/>
     </row>
-    <row r="84" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A84" s="12"/>
       <c r="B84" s="12"/>
       <c r="C84" s="4"/>
@@ -3343,7 +3342,7 @@
       <c r="S84" s="8"/>
       <c r="T84" s="8"/>
     </row>
-    <row r="85" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A85" s="12"/>
       <c r="B85" s="12"/>
       <c r="C85" s="4"/>
@@ -3365,7 +3364,7 @@
       <c r="S85" s="8"/>
       <c r="T85" s="8"/>
     </row>
-    <row r="86" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A86" s="12"/>
       <c r="B86" s="12"/>
       <c r="C86" s="4"/>
@@ -3387,7 +3386,7 @@
       <c r="S86" s="8"/>
       <c r="T86" s="8"/>
     </row>
-    <row r="87" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A87" s="12"/>
       <c r="B87" s="12"/>
       <c r="C87" s="4"/>
@@ -3409,7 +3408,7 @@
       <c r="S87" s="8"/>
       <c r="T87" s="8"/>
     </row>
-    <row r="88" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A88" s="12"/>
       <c r="B88" s="12"/>
       <c r="C88" s="4"/>
@@ -3431,7 +3430,7 @@
       <c r="S88" s="8"/>
       <c r="T88" s="8"/>
     </row>
-    <row r="89" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A89" s="12"/>
       <c r="B89" s="12"/>
       <c r="C89" s="4"/>
@@ -3453,7 +3452,7 @@
       <c r="S89" s="8"/>
       <c r="T89" s="8"/>
     </row>
-    <row r="90" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A90" s="12"/>
       <c r="B90" s="12"/>
       <c r="C90" s="4"/>
@@ -3475,7 +3474,7 @@
       <c r="S90" s="8"/>
       <c r="T90" s="8"/>
     </row>
-    <row r="91" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A91" s="12"/>
       <c r="B91" s="12"/>
       <c r="C91" s="4"/>
@@ -3497,7 +3496,7 @@
       <c r="S91" s="8"/>
       <c r="T91" s="8"/>
     </row>
-    <row r="92" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A92" s="12"/>
       <c r="B92" s="12"/>
       <c r="C92" s="4"/>
@@ -3519,7 +3518,7 @@
       <c r="S92" s="8"/>
       <c r="T92" s="8"/>
     </row>
-    <row r="93" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A93" s="12"/>
       <c r="B93" s="12"/>
       <c r="C93" s="4"/>
@@ -3541,7 +3540,7 @@
       <c r="S93" s="8"/>
       <c r="T93" s="8"/>
     </row>
-    <row r="94" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A94" s="12"/>
       <c r="B94" s="12"/>
       <c r="C94" s="4"/>
@@ -3563,7 +3562,7 @@
       <c r="S94" s="8"/>
       <c r="T94" s="8"/>
     </row>
-    <row r="95" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A95" s="12"/>
       <c r="B95" s="12"/>
       <c r="C95" s="4"/>
@@ -3585,7 +3584,7 @@
       <c r="S95" s="8"/>
       <c r="T95" s="8"/>
     </row>
-    <row r="96" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A96" s="12"/>
       <c r="B96" s="12"/>
       <c r="C96" s="4"/>
@@ -3607,7 +3606,7 @@
       <c r="S96" s="8"/>
       <c r="T96" s="8"/>
     </row>
-    <row r="97" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A97" s="12"/>
       <c r="B97" s="12"/>
       <c r="C97" s="4"/>
@@ -3629,7 +3628,7 @@
       <c r="S97" s="8"/>
       <c r="T97" s="8"/>
     </row>
-    <row r="98" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A98" s="12"/>
       <c r="B98" s="12"/>
       <c r="C98" s="4"/>
@@ -3651,7 +3650,7 @@
       <c r="S98" s="8"/>
       <c r="T98" s="8"/>
     </row>
-    <row r="99" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A99" s="12"/>
       <c r="B99" s="12"/>
       <c r="C99" s="4"/>
@@ -3673,7 +3672,7 @@
       <c r="S99" s="8"/>
       <c r="T99" s="8"/>
     </row>
-    <row r="100" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A100" s="12"/>
       <c r="B100" s="12"/>
       <c r="C100" s="4"/>
@@ -3695,7 +3694,7 @@
       <c r="S100" s="8"/>
       <c r="T100" s="8"/>
     </row>
-    <row r="101" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A101" s="12"/>
       <c r="B101" s="12"/>
       <c r="C101" s="4"/>
@@ -3717,7 +3716,7 @@
       <c r="S101" s="8"/>
       <c r="T101" s="8"/>
     </row>
-    <row r="102" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A102" s="12"/>
       <c r="B102" s="12"/>
       <c r="C102" s="4"/>
@@ -3739,7 +3738,7 @@
       <c r="S102" s="8"/>
       <c r="T102" s="8"/>
     </row>
-    <row r="103" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A103" s="12"/>
       <c r="B103" s="12"/>
       <c r="C103" s="4"/>
@@ -3761,7 +3760,7 @@
       <c r="S103" s="8"/>
       <c r="T103" s="8"/>
     </row>
-    <row r="104" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A104" s="12"/>
       <c r="B104" s="12"/>
       <c r="C104" s="4"/>
@@ -3783,7 +3782,7 @@
       <c r="S104" s="8"/>
       <c r="T104" s="8"/>
     </row>
-    <row r="105" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A105" s="12"/>
       <c r="B105" s="12"/>
       <c r="C105" s="4"/>
@@ -3805,7 +3804,7 @@
       <c r="S105" s="8"/>
       <c r="T105" s="8"/>
     </row>
-    <row r="106" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A106" s="12"/>
       <c r="B106" s="12"/>
       <c r="C106" s="4"/>
@@ -3827,7 +3826,7 @@
       <c r="S106" s="8"/>
       <c r="T106" s="8"/>
     </row>
-    <row r="107" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A107" s="12"/>
       <c r="B107" s="12"/>
       <c r="C107" s="4"/>
@@ -3849,7 +3848,7 @@
       <c r="S107" s="8"/>
       <c r="T107" s="8"/>
     </row>
-    <row r="108" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A108" s="12"/>
       <c r="B108" s="12"/>
       <c r="C108" s="4"/>
@@ -3871,7 +3870,7 @@
       <c r="S108" s="8"/>
       <c r="T108" s="8"/>
     </row>
-    <row r="109" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A109" s="12"/>
       <c r="B109" s="12"/>
       <c r="C109" s="4"/>
@@ -3893,7 +3892,7 @@
       <c r="S109" s="8"/>
       <c r="T109" s="8"/>
     </row>
-    <row r="110" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A110" s="12"/>
       <c r="B110" s="12"/>
       <c r="C110" s="4"/>
@@ -3915,7 +3914,7 @@
       <c r="S110" s="8"/>
       <c r="T110" s="8"/>
     </row>
-    <row r="111" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A111" s="12"/>
       <c r="B111" s="12"/>
       <c r="C111" s="4"/>
@@ -3937,7 +3936,7 @@
       <c r="S111" s="8"/>
       <c r="T111" s="8"/>
     </row>
-    <row r="112" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A112" s="12"/>
       <c r="B112" s="12"/>
       <c r="C112" s="4"/>
@@ -3959,7 +3958,7 @@
       <c r="S112" s="8"/>
       <c r="T112" s="8"/>
     </row>
-    <row r="113" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A113" s="12"/>
       <c r="B113" s="12"/>
       <c r="C113" s="4"/>
@@ -3981,7 +3980,7 @@
       <c r="S113" s="8"/>
       <c r="T113" s="8"/>
     </row>
-    <row r="114" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A114" s="12"/>
       <c r="B114" s="12"/>
       <c r="C114" s="4"/>
@@ -4003,7 +4002,7 @@
       <c r="S114" s="8"/>
       <c r="T114" s="8"/>
     </row>
-    <row r="115" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A115" s="12"/>
       <c r="B115" s="12"/>
       <c r="C115" s="4"/>
@@ -4025,7 +4024,7 @@
       <c r="S115" s="8"/>
       <c r="T115" s="8"/>
     </row>
-    <row r="116" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A116" s="12"/>
       <c r="B116" s="12"/>
       <c r="C116" s="4"/>
@@ -4047,7 +4046,7 @@
       <c r="S116" s="8"/>
       <c r="T116" s="8"/>
     </row>
-    <row r="117" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A117" s="12"/>
       <c r="B117" s="12"/>
       <c r="C117" s="4"/>
@@ -4069,7 +4068,7 @@
       <c r="S117" s="8"/>
       <c r="T117" s="8"/>
     </row>
-    <row r="118" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A118" s="12"/>
       <c r="B118" s="12"/>
       <c r="C118" s="4"/>
@@ -4091,7 +4090,7 @@
       <c r="S118" s="8"/>
       <c r="T118" s="8"/>
     </row>
-    <row r="119" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A119" s="12"/>
       <c r="B119" s="12"/>
       <c r="C119" s="4"/>
@@ -4113,7 +4112,7 @@
       <c r="S119" s="8"/>
       <c r="T119" s="8"/>
     </row>
-    <row r="120" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A120" s="12"/>
       <c r="B120" s="12"/>
       <c r="C120" s="4"/>
@@ -4135,7 +4134,7 @@
       <c r="S120" s="8"/>
       <c r="T120" s="8"/>
     </row>
-    <row r="121" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A121" s="12"/>
       <c r="B121" s="12"/>
       <c r="C121" s="4"/>
@@ -4157,7 +4156,7 @@
       <c r="S121" s="8"/>
       <c r="T121" s="8"/>
     </row>
-    <row r="122" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A122" s="12"/>
       <c r="B122" s="12"/>
       <c r="C122" s="4"/>
@@ -4179,7 +4178,7 @@
       <c r="S122" s="8"/>
       <c r="T122" s="8"/>
     </row>
-    <row r="123" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A123" s="12"/>
       <c r="B123" s="12"/>
       <c r="C123" s="4"/>
@@ -4201,7 +4200,7 @@
       <c r="S123" s="8"/>
       <c r="T123" s="8"/>
     </row>
-    <row r="124" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A124" s="12"/>
       <c r="B124" s="12"/>
       <c r="C124" s="4"/>
@@ -4223,7 +4222,7 @@
       <c r="S124" s="8"/>
       <c r="T124" s="8"/>
     </row>
-    <row r="125" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A125" s="12"/>
       <c r="B125" s="12"/>
       <c r="C125" s="4"/>
@@ -4245,7 +4244,7 @@
       <c r="S125" s="8"/>
       <c r="T125" s="8"/>
     </row>
-    <row r="126" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A126" s="12"/>
       <c r="B126" s="12"/>
       <c r="C126" s="4"/>
@@ -4267,7 +4266,7 @@
       <c r="S126" s="8"/>
       <c r="T126" s="8"/>
     </row>
-    <row r="127" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A127" s="12"/>
       <c r="B127" s="12"/>
       <c r="C127" s="4"/>
@@ -4289,7 +4288,7 @@
       <c r="S127" s="8"/>
       <c r="T127" s="8"/>
     </row>
-    <row r="128" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A128" s="12"/>
       <c r="B128" s="12"/>
       <c r="C128" s="4"/>
@@ -4311,7 +4310,7 @@
       <c r="S128" s="8"/>
       <c r="T128" s="8"/>
     </row>
-    <row r="129" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A129" s="12"/>
       <c r="B129" s="12"/>
       <c r="C129" s="4"/>
@@ -4333,7 +4332,7 @@
       <c r="S129" s="8"/>
       <c r="T129" s="8"/>
     </row>
-    <row r="130" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A130" s="12"/>
       <c r="B130" s="12"/>
       <c r="C130" s="4"/>
@@ -4355,7 +4354,7 @@
       <c r="S130" s="8"/>
       <c r="T130" s="8"/>
     </row>
-    <row r="131" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A131" s="12"/>
       <c r="B131" s="12"/>
       <c r="C131" s="4"/>
@@ -4377,7 +4376,7 @@
       <c r="S131" s="8"/>
       <c r="T131" s="8"/>
     </row>
-    <row r="132" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A132" s="12"/>
       <c r="B132" s="12"/>
       <c r="C132" s="4"/>
@@ -4399,7 +4398,7 @@
       <c r="S132" s="8"/>
       <c r="T132" s="8"/>
     </row>
-    <row r="133" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A133" s="12"/>
       <c r="B133" s="12"/>
       <c r="C133" s="4"/>
@@ -4421,7 +4420,7 @@
       <c r="S133" s="8"/>
       <c r="T133" s="8"/>
     </row>
-    <row r="134" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A134" s="12"/>
       <c r="B134" s="12"/>
       <c r="C134" s="4"/>
@@ -4443,7 +4442,7 @@
       <c r="S134" s="8"/>
       <c r="T134" s="8"/>
     </row>
-    <row r="135" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A135" s="12"/>
       <c r="B135" s="12"/>
       <c r="C135" s="4"/>
@@ -4465,7 +4464,7 @@
       <c r="S135" s="8"/>
       <c r="T135" s="8"/>
     </row>
-    <row r="136" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A136" s="12"/>
       <c r="B136" s="12"/>
       <c r="C136" s="4"/>
@@ -4487,7 +4486,7 @@
       <c r="S136" s="8"/>
       <c r="T136" s="8"/>
     </row>
-    <row r="137" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A137" s="12"/>
       <c r="B137" s="12"/>
       <c r="C137" s="4"/>
@@ -4509,7 +4508,7 @@
       <c r="S137" s="8"/>
       <c r="T137" s="8"/>
     </row>
-    <row r="138" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A138" s="12"/>
       <c r="B138" s="12"/>
       <c r="C138" s="4"/>
@@ -4531,7 +4530,7 @@
       <c r="S138" s="8"/>
       <c r="T138" s="8"/>
     </row>
-    <row r="139" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A139" s="12"/>
       <c r="B139" s="12"/>
       <c r="C139" s="4"/>
@@ -4553,7 +4552,7 @@
       <c r="S139" s="8"/>
       <c r="T139" s="8"/>
     </row>
-    <row r="140" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A140" s="12"/>
       <c r="B140" s="12"/>
       <c r="C140" s="4"/>
@@ -4575,7 +4574,7 @@
       <c r="S140" s="8"/>
       <c r="T140" s="8"/>
     </row>
-    <row r="141" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A141" s="12"/>
       <c r="B141" s="12"/>
       <c r="C141" s="4"/>
@@ -4597,7 +4596,7 @@
       <c r="S141" s="8"/>
       <c r="T141" s="8"/>
     </row>
-    <row r="142" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A142" s="12"/>
       <c r="B142" s="12"/>
       <c r="C142" s="4"/>
@@ -4619,7 +4618,7 @@
       <c r="S142" s="8"/>
       <c r="T142" s="8"/>
     </row>
-    <row r="143" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A143" s="12"/>
       <c r="B143" s="12"/>
       <c r="C143" s="4"/>
@@ -4641,7 +4640,7 @@
       <c r="S143" s="8"/>
       <c r="T143" s="8"/>
     </row>
-    <row r="144" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A144" s="12"/>
       <c r="B144" s="12"/>
       <c r="C144" s="4"/>
@@ -4663,7 +4662,7 @@
       <c r="S144" s="8"/>
       <c r="T144" s="8"/>
     </row>
-    <row r="145" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A145" s="12"/>
       <c r="B145" s="12"/>
       <c r="C145" s="4"/>
@@ -4685,7 +4684,7 @@
       <c r="S145" s="8"/>
       <c r="T145" s="8"/>
     </row>
-    <row r="146" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A146" s="12"/>
       <c r="B146" s="12"/>
       <c r="C146" s="4"/>
@@ -4707,7 +4706,7 @@
       <c r="S146" s="8"/>
       <c r="T146" s="8"/>
     </row>
-    <row r="147" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A147" s="12"/>
       <c r="B147" s="12"/>
       <c r="C147" s="4"/>
@@ -4729,7 +4728,7 @@
       <c r="S147" s="8"/>
       <c r="T147" s="8"/>
     </row>
-    <row r="148" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A148" s="12"/>
       <c r="B148" s="12"/>
       <c r="C148" s="4"/>
@@ -4751,7 +4750,7 @@
       <c r="S148" s="8"/>
       <c r="T148" s="8"/>
     </row>
-    <row r="149" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A149" s="12"/>
       <c r="B149" s="12"/>
       <c r="C149" s="4"/>
@@ -4773,7 +4772,7 @@
       <c r="S149" s="8"/>
       <c r="T149" s="8"/>
     </row>
-    <row r="150" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A150" s="12"/>
       <c r="B150" s="12"/>
       <c r="C150" s="4"/>
@@ -4795,7 +4794,7 @@
       <c r="S150" s="8"/>
       <c r="T150" s="8"/>
     </row>
-    <row r="151" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A151" s="12"/>
       <c r="B151" s="12"/>
       <c r="C151" s="4"/>
@@ -4817,7 +4816,7 @@
       <c r="S151" s="8"/>
       <c r="T151" s="8"/>
     </row>
-    <row r="152" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A152" s="12"/>
       <c r="B152" s="12"/>
       <c r="C152" s="4"/>
@@ -4839,7 +4838,7 @@
       <c r="S152" s="8"/>
       <c r="T152" s="8"/>
     </row>
-    <row r="153" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A153" s="12"/>
       <c r="B153" s="12"/>
       <c r="C153" s="4"/>
@@ -4861,7 +4860,7 @@
       <c r="S153" s="8"/>
       <c r="T153" s="8"/>
     </row>
-    <row r="154" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A154" s="12"/>
       <c r="B154" s="12"/>
       <c r="C154" s="4"/>
@@ -4883,7 +4882,7 @@
       <c r="S154" s="8"/>
       <c r="T154" s="8"/>
     </row>
-    <row r="155" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A155" s="12"/>
       <c r="B155" s="12"/>
       <c r="C155" s="4"/>
@@ -4905,7 +4904,7 @@
       <c r="S155" s="8"/>
       <c r="T155" s="8"/>
     </row>
-    <row r="156" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A156" s="12"/>
       <c r="B156" s="12"/>
       <c r="C156" s="4"/>
@@ -4927,7 +4926,7 @@
       <c r="S156" s="8"/>
       <c r="T156" s="8"/>
     </row>
-    <row r="157" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A157" s="12"/>
       <c r="B157" s="12"/>
       <c r="C157" s="4"/>
@@ -4949,7 +4948,7 @@
       <c r="S157" s="8"/>
       <c r="T157" s="8"/>
     </row>
-    <row r="158" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A158" s="12"/>
       <c r="B158" s="12"/>
       <c r="C158" s="4"/>
@@ -4971,7 +4970,7 @@
       <c r="S158" s="8"/>
       <c r="T158" s="8"/>
     </row>
-    <row r="159" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A159" s="12"/>
       <c r="B159" s="12"/>
       <c r="C159" s="4"/>
@@ -4993,7 +4992,7 @@
       <c r="S159" s="8"/>
       <c r="T159" s="8"/>
     </row>
-    <row r="160" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A160" s="12"/>
       <c r="B160" s="12"/>
       <c r="C160" s="4"/>
@@ -5015,7 +5014,7 @@
       <c r="S160" s="8"/>
       <c r="T160" s="8"/>
     </row>
-    <row r="161" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A161" s="12"/>
       <c r="B161" s="12"/>
       <c r="C161" s="4"/>
@@ -5037,7 +5036,7 @@
       <c r="S161" s="8"/>
       <c r="T161" s="8"/>
     </row>
-    <row r="162" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A162" s="12"/>
       <c r="B162" s="12"/>
       <c r="C162" s="4"/>
@@ -5059,7 +5058,7 @@
       <c r="S162" s="8"/>
       <c r="T162" s="8"/>
     </row>
-    <row r="163" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A163" s="12"/>
       <c r="B163" s="12"/>
       <c r="C163" s="4"/>
@@ -5081,7 +5080,7 @@
       <c r="S163" s="8"/>
       <c r="T163" s="8"/>
     </row>
-    <row r="164" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A164" s="12"/>
       <c r="B164" s="12"/>
       <c r="C164" s="4"/>
@@ -5103,7 +5102,7 @@
       <c r="S164" s="8"/>
       <c r="T164" s="8"/>
     </row>
-    <row r="165" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A165" s="12"/>
       <c r="B165" s="12"/>
       <c r="C165" s="4"/>
@@ -5125,7 +5124,7 @@
       <c r="S165" s="8"/>
       <c r="T165" s="8"/>
     </row>
-    <row r="166" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A166" s="12"/>
       <c r="B166" s="12"/>
       <c r="C166" s="4"/>
@@ -5147,7 +5146,7 @@
       <c r="S166" s="8"/>
       <c r="T166" s="8"/>
     </row>
-    <row r="167" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A167" s="12"/>
       <c r="B167" s="12"/>
       <c r="C167" s="4"/>
@@ -5169,7 +5168,7 @@
       <c r="S167" s="8"/>
       <c r="T167" s="8"/>
     </row>
-    <row r="168" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A168" s="12"/>
       <c r="B168" s="12"/>
       <c r="C168" s="4"/>
@@ -5191,7 +5190,7 @@
       <c r="S168" s="8"/>
       <c r="T168" s="8"/>
     </row>
-    <row r="169" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A169" s="12"/>
       <c r="B169" s="12"/>
       <c r="C169" s="4"/>
@@ -5213,7 +5212,7 @@
       <c r="S169" s="8"/>
       <c r="T169" s="8"/>
     </row>
-    <row r="170" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A170" s="12"/>
       <c r="B170" s="12"/>
       <c r="C170" s="4"/>
@@ -5235,7 +5234,7 @@
       <c r="S170" s="8"/>
       <c r="T170" s="8"/>
     </row>
-    <row r="171" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A171" s="12"/>
       <c r="B171" s="12"/>
       <c r="C171" s="4"/>
@@ -5257,7 +5256,7 @@
       <c r="S171" s="8"/>
       <c r="T171" s="8"/>
     </row>
-    <row r="172" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A172" s="12"/>
       <c r="B172" s="12"/>
       <c r="C172" s="4"/>
@@ -5279,7 +5278,7 @@
       <c r="S172" s="8"/>
       <c r="T172" s="8"/>
     </row>
-    <row r="173" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A173" s="12"/>
       <c r="B173" s="12"/>
       <c r="C173" s="4"/>
@@ -5301,7 +5300,7 @@
       <c r="S173" s="8"/>
       <c r="T173" s="8"/>
     </row>
-    <row r="174" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A174" s="12"/>
       <c r="B174" s="12"/>
       <c r="C174" s="4"/>
@@ -5323,7 +5322,7 @@
       <c r="S174" s="8"/>
       <c r="T174" s="8"/>
     </row>
-    <row r="175" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A175" s="12"/>
       <c r="B175" s="12"/>
       <c r="C175" s="4"/>
@@ -5345,7 +5344,7 @@
       <c r="S175" s="8"/>
       <c r="T175" s="8"/>
     </row>
-    <row r="176" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A176" s="12"/>
       <c r="B176" s="12"/>
       <c r="C176" s="4"/>
@@ -5367,7 +5366,7 @@
       <c r="S176" s="8"/>
       <c r="T176" s="8"/>
     </row>
-    <row r="177" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A177" s="12"/>
       <c r="B177" s="12"/>
       <c r="C177" s="4"/>
@@ -5389,7 +5388,7 @@
       <c r="S177" s="8"/>
       <c r="T177" s="8"/>
     </row>
-    <row r="178" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A178" s="12"/>
       <c r="B178" s="12"/>
       <c r="C178" s="4"/>
@@ -5411,7 +5410,7 @@
       <c r="S178" s="8"/>
       <c r="T178" s="8"/>
     </row>
-    <row r="179" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A179" s="12"/>
       <c r="B179" s="12"/>
       <c r="C179" s="4"/>
@@ -5433,7 +5432,7 @@
       <c r="S179" s="8"/>
       <c r="T179" s="8"/>
     </row>
-    <row r="180" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A180" s="12"/>
       <c r="B180" s="12"/>
       <c r="C180" s="4"/>
@@ -5455,7 +5454,7 @@
       <c r="S180" s="8"/>
       <c r="T180" s="8"/>
     </row>
-    <row r="181" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A181" s="12"/>
       <c r="B181" s="12"/>
       <c r="C181" s="4"/>
@@ -5477,7 +5476,7 @@
       <c r="S181" s="8"/>
       <c r="T181" s="8"/>
     </row>
-    <row r="182" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A182" s="12"/>
       <c r="B182" s="12"/>
       <c r="C182" s="4"/>
@@ -5499,7 +5498,7 @@
       <c r="S182" s="8"/>
       <c r="T182" s="8"/>
     </row>
-    <row r="183" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A183" s="12"/>
       <c r="B183" s="12"/>
       <c r="C183" s="4"/>
@@ -5521,7 +5520,7 @@
       <c r="S183" s="8"/>
       <c r="T183" s="8"/>
     </row>
-    <row r="184" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A184" s="12"/>
       <c r="B184" s="12"/>
       <c r="C184" s="4"/>
@@ -5543,7 +5542,7 @@
       <c r="S184" s="8"/>
       <c r="T184" s="8"/>
     </row>
-    <row r="185" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A185" s="12"/>
       <c r="B185" s="12"/>
       <c r="C185" s="4"/>
@@ -5565,7 +5564,7 @@
       <c r="S185" s="8"/>
       <c r="T185" s="8"/>
     </row>
-    <row r="186" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A186" s="12"/>
       <c r="B186" s="12"/>
       <c r="C186" s="4"/>
@@ -5587,7 +5586,7 @@
       <c r="S186" s="8"/>
       <c r="T186" s="8"/>
     </row>
-    <row r="187" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A187" s="12"/>
       <c r="B187" s="12"/>
       <c r="C187" s="4"/>
@@ -5609,7 +5608,7 @@
       <c r="S187" s="8"/>
       <c r="T187" s="8"/>
     </row>
-    <row r="188" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A188" s="12"/>
       <c r="B188" s="12"/>
       <c r="C188" s="4"/>
@@ -5631,7 +5630,7 @@
       <c r="S188" s="8"/>
       <c r="T188" s="8"/>
     </row>
-    <row r="189" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A189" s="12"/>
       <c r="B189" s="12"/>
       <c r="C189" s="4"/>
@@ -5653,7 +5652,7 @@
       <c r="S189" s="8"/>
       <c r="T189" s="8"/>
     </row>
-    <row r="190" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A190" s="12"/>
       <c r="B190" s="12"/>
       <c r="C190" s="4"/>
@@ -5675,7 +5674,7 @@
       <c r="S190" s="8"/>
       <c r="T190" s="8"/>
     </row>
-    <row r="191" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A191" s="12"/>
       <c r="B191" s="12"/>
       <c r="C191" s="4"/>
@@ -5697,7 +5696,7 @@
       <c r="S191" s="8"/>
       <c r="T191" s="8"/>
     </row>
-    <row r="192" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A192" s="12"/>
       <c r="B192" s="12"/>
       <c r="C192" s="4"/>
@@ -5719,7 +5718,7 @@
       <c r="S192" s="8"/>
       <c r="T192" s="8"/>
     </row>
-    <row r="193" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A193" s="12"/>
       <c r="B193" s="12"/>
       <c r="C193" s="4"/>
@@ -5741,7 +5740,7 @@
       <c r="S193" s="8"/>
       <c r="T193" s="8"/>
     </row>
-    <row r="194" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A194" s="12"/>
       <c r="B194" s="12"/>
       <c r="C194" s="4"/>
@@ -5763,7 +5762,7 @@
       <c r="S194" s="8"/>
       <c r="T194" s="8"/>
     </row>
-    <row r="195" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A195" s="12"/>
       <c r="B195" s="12"/>
       <c r="C195" s="4"/>
@@ -5785,7 +5784,7 @@
       <c r="S195" s="8"/>
       <c r="T195" s="8"/>
     </row>
-    <row r="196" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A196" s="12"/>
       <c r="B196" s="12"/>
       <c r="C196" s="4"/>
@@ -5807,7 +5806,7 @@
       <c r="S196" s="8"/>
       <c r="T196" s="8"/>
     </row>
-    <row r="197" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A197" s="12"/>
       <c r="B197" s="12"/>
       <c r="C197" s="4"/>
@@ -5829,7 +5828,7 @@
       <c r="S197" s="8"/>
       <c r="T197" s="8"/>
     </row>
-    <row r="198" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A198" s="12"/>
       <c r="B198" s="12"/>
       <c r="C198" s="4"/>
@@ -5851,7 +5850,7 @@
       <c r="S198" s="8"/>
       <c r="T198" s="8"/>
     </row>
-    <row r="199" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A199" s="12"/>
       <c r="B199" s="12"/>
       <c r="C199" s="4"/>
@@ -5873,7 +5872,7 @@
       <c r="S199" s="8"/>
       <c r="T199" s="8"/>
     </row>
-    <row r="200" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A200" s="12"/>
       <c r="B200" s="12"/>
       <c r="C200" s="4"/>
@@ -5895,7 +5894,7 @@
       <c r="S200" s="8"/>
       <c r="T200" s="8"/>
     </row>
-    <row r="201" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A201" s="12"/>
       <c r="B201" s="12"/>
       <c r="C201" s="4"/>
@@ -5917,7 +5916,7 @@
       <c r="S201" s="8"/>
       <c r="T201" s="8"/>
     </row>
-    <row r="202" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A202" s="12"/>
       <c r="B202" s="12"/>
       <c r="C202" s="4"/>
@@ -5939,7 +5938,7 @@
       <c r="S202" s="8"/>
       <c r="T202" s="8"/>
     </row>
-    <row r="203" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A203" s="12"/>
       <c r="B203" s="12"/>
       <c r="C203" s="4"/>
@@ -5961,7 +5960,7 @@
       <c r="S203" s="8"/>
       <c r="T203" s="8"/>
     </row>
-    <row r="204" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A204" s="12"/>
       <c r="B204" s="12"/>
       <c r="C204" s="4"/>
@@ -5983,7 +5982,7 @@
       <c r="S204" s="8"/>
       <c r="T204" s="8"/>
     </row>
-    <row r="205" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A205" s="12"/>
       <c r="B205" s="12"/>
       <c r="C205" s="4"/>
@@ -6005,7 +6004,7 @@
       <c r="S205" s="8"/>
       <c r="T205" s="8"/>
     </row>
-    <row r="206" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A206" s="12"/>
       <c r="B206" s="12"/>
       <c r="C206" s="4"/>
@@ -6027,7 +6026,7 @@
       <c r="S206" s="8"/>
       <c r="T206" s="8"/>
     </row>
-    <row r="207" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A207" s="12"/>
       <c r="B207" s="12"/>
       <c r="C207" s="4"/>
@@ -6049,7 +6048,7 @@
       <c r="S207" s="8"/>
       <c r="T207" s="8"/>
     </row>
-    <row r="208" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A208" s="12"/>
       <c r="B208" s="12"/>
       <c r="C208" s="4"/>
@@ -6071,7 +6070,7 @@
       <c r="S208" s="8"/>
       <c r="T208" s="8"/>
     </row>
-    <row r="209" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A209" s="12"/>
       <c r="B209" s="12"/>
       <c r="C209" s="4"/>
@@ -6093,7 +6092,7 @@
       <c r="S209" s="8"/>
       <c r="T209" s="8"/>
     </row>
-    <row r="210" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A210" s="12"/>
       <c r="B210" s="12"/>
       <c r="C210" s="4"/>
@@ -6115,7 +6114,7 @@
       <c r="S210" s="8"/>
       <c r="T210" s="8"/>
     </row>
-    <row r="211" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A211" s="12"/>
       <c r="B211" s="12"/>
       <c r="C211" s="4"/>
@@ -6137,7 +6136,7 @@
       <c r="S211" s="8"/>
       <c r="T211" s="8"/>
     </row>
-    <row r="212" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A212" s="12"/>
       <c r="B212" s="12"/>
       <c r="C212" s="4"/>
@@ -6159,7 +6158,7 @@
       <c r="S212" s="8"/>
       <c r="T212" s="8"/>
     </row>
-    <row r="213" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A213" s="12"/>
       <c r="B213" s="12"/>
       <c r="C213" s="4"/>
@@ -6181,7 +6180,7 @@
       <c r="S213" s="8"/>
       <c r="T213" s="8"/>
     </row>
-    <row r="214" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A214" s="12"/>
       <c r="B214" s="12"/>
       <c r="C214" s="4"/>
@@ -6203,7 +6202,7 @@
       <c r="S214" s="8"/>
       <c r="T214" s="8"/>
     </row>
-    <row r="215" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A215" s="12"/>
       <c r="B215" s="12"/>
       <c r="C215" s="4"/>
@@ -6225,7 +6224,7 @@
       <c r="S215" s="8"/>
       <c r="T215" s="8"/>
     </row>
-    <row r="216" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A216" s="12"/>
       <c r="B216" s="12"/>
       <c r="C216" s="4"/>
@@ -6247,7 +6246,7 @@
       <c r="S216" s="8"/>
       <c r="T216" s="8"/>
     </row>
-    <row r="217" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A217" s="12"/>
       <c r="B217" s="12"/>
       <c r="C217" s="4"/>
@@ -6269,7 +6268,7 @@
       <c r="S217" s="8"/>
       <c r="T217" s="8"/>
     </row>
-    <row r="218" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A218" s="12"/>
       <c r="B218" s="12"/>
       <c r="C218" s="4"/>
@@ -6291,7 +6290,7 @@
       <c r="S218" s="8"/>
       <c r="T218" s="8"/>
     </row>
-    <row r="219" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A219" s="12"/>
       <c r="B219" s="12"/>
       <c r="C219" s="4"/>
@@ -6313,7 +6312,7 @@
       <c r="S219" s="8"/>
       <c r="T219" s="8"/>
     </row>
-    <row r="220" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A220" s="12"/>
       <c r="B220" s="12"/>
       <c r="C220" s="4"/>
@@ -6335,7 +6334,7 @@
       <c r="S220" s="8"/>
       <c r="T220" s="8"/>
     </row>
-    <row r="221" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A221" s="12"/>
       <c r="B221" s="12"/>
       <c r="C221" s="4"/>
@@ -6357,7 +6356,7 @@
       <c r="S221" s="8"/>
       <c r="T221" s="8"/>
     </row>
-    <row r="222" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A222" s="12"/>
       <c r="B222" s="12"/>
       <c r="C222" s="4"/>
@@ -6379,7 +6378,7 @@
       <c r="S222" s="8"/>
       <c r="T222" s="8"/>
     </row>
-    <row r="223" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A223" s="12"/>
       <c r="B223" s="12"/>
       <c r="C223" s="4"/>
@@ -6401,7 +6400,7 @@
       <c r="S223" s="8"/>
       <c r="T223" s="8"/>
     </row>
-    <row r="224" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A224" s="12"/>
       <c r="B224" s="12"/>
       <c r="C224" s="4"/>
@@ -6423,7 +6422,7 @@
       <c r="S224" s="8"/>
       <c r="T224" s="8"/>
     </row>
-    <row r="225" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A225" s="12"/>
       <c r="B225" s="12"/>
       <c r="C225" s="4"/>
@@ -6445,7 +6444,7 @@
       <c r="S225" s="8"/>
       <c r="T225" s="8"/>
     </row>
-    <row r="226" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A226" s="12"/>
       <c r="B226" s="12"/>
       <c r="C226" s="4"/>
@@ -6467,7 +6466,7 @@
       <c r="S226" s="8"/>
       <c r="T226" s="8"/>
     </row>
-    <row r="227" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A227" s="12"/>
       <c r="B227" s="12"/>
       <c r="C227" s="4"/>
@@ -6489,7 +6488,7 @@
       <c r="S227" s="8"/>
       <c r="T227" s="8"/>
     </row>
-    <row r="228" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A228" s="12"/>
       <c r="B228" s="12"/>
       <c r="C228" s="4"/>
@@ -6511,7 +6510,7 @@
       <c r="S228" s="8"/>
       <c r="T228" s="8"/>
     </row>
-    <row r="229" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A229" s="12"/>
       <c r="B229" s="12"/>
       <c r="C229" s="4"/>
@@ -6533,7 +6532,7 @@
       <c r="S229" s="8"/>
       <c r="T229" s="8"/>
     </row>
-    <row r="230" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A230" s="12"/>
       <c r="B230" s="12"/>
       <c r="C230" s="4"/>
@@ -6555,7 +6554,7 @@
       <c r="S230" s="8"/>
       <c r="T230" s="8"/>
     </row>
-    <row r="231" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A231" s="12"/>
       <c r="B231" s="12"/>
       <c r="C231" s="4"/>
@@ -6577,7 +6576,7 @@
       <c r="S231" s="8"/>
       <c r="T231" s="8"/>
     </row>
-    <row r="232" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A232" s="12"/>
       <c r="B232" s="12"/>
       <c r="C232" s="4"/>
@@ -6599,7 +6598,7 @@
       <c r="S232" s="8"/>
       <c r="T232" s="8"/>
     </row>
-    <row r="233" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A233" s="12"/>
       <c r="B233" s="12"/>
       <c r="C233" s="4"/>
@@ -6621,7 +6620,7 @@
       <c r="S233" s="8"/>
       <c r="T233" s="8"/>
     </row>
-    <row r="234" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A234" s="12"/>
       <c r="B234" s="12"/>
       <c r="C234" s="4"/>
@@ -6643,7 +6642,7 @@
       <c r="S234" s="8"/>
       <c r="T234" s="8"/>
     </row>
-    <row r="235" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A235" s="12"/>
       <c r="B235" s="12"/>
       <c r="C235" s="4"/>
@@ -6665,7 +6664,7 @@
       <c r="S235" s="8"/>
       <c r="T235" s="8"/>
     </row>
-    <row r="236" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A236" s="12"/>
       <c r="B236" s="12"/>
       <c r="C236" s="4"/>
@@ -6687,7 +6686,7 @@
       <c r="S236" s="8"/>
       <c r="T236" s="8"/>
     </row>
-    <row r="237" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A237" s="12"/>
       <c r="B237" s="12"/>
       <c r="C237" s="4"/>
@@ -6709,7 +6708,7 @@
       <c r="S237" s="8"/>
       <c r="T237" s="8"/>
     </row>
-    <row r="238" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A238" s="12"/>
       <c r="B238" s="12"/>
       <c r="C238" s="4"/>
@@ -6731,7 +6730,7 @@
       <c r="S238" s="8"/>
       <c r="T238" s="8"/>
     </row>
-    <row r="239" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A239" s="12"/>
       <c r="B239" s="12"/>
       <c r="C239" s="4"/>
@@ -6753,7 +6752,7 @@
       <c r="S239" s="8"/>
       <c r="T239" s="8"/>
     </row>
-    <row r="240" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A240" s="12"/>
       <c r="B240" s="12"/>
       <c r="C240" s="4"/>
@@ -6775,7 +6774,7 @@
       <c r="S240" s="8"/>
       <c r="T240" s="8"/>
     </row>
-    <row r="241" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A241" s="12"/>
       <c r="B241" s="12"/>
       <c r="C241" s="4"/>
@@ -6797,7 +6796,7 @@
       <c r="S241" s="8"/>
       <c r="T241" s="8"/>
     </row>
-    <row r="242" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A242" s="12"/>
       <c r="B242" s="12"/>
       <c r="C242" s="4"/>
@@ -6819,7 +6818,7 @@
       <c r="S242" s="8"/>
       <c r="T242" s="8"/>
     </row>
-    <row r="243" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A243" s="12"/>
       <c r="B243" s="12"/>
       <c r="C243" s="4"/>
@@ -6841,7 +6840,7 @@
       <c r="S243" s="8"/>
       <c r="T243" s="8"/>
     </row>
-    <row r="244" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A244" s="12"/>
       <c r="B244" s="12"/>
       <c r="C244" s="4"/>
@@ -6863,7 +6862,7 @@
       <c r="S244" s="8"/>
       <c r="T244" s="8"/>
     </row>
-    <row r="245" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A245" s="12"/>
       <c r="B245" s="12"/>
       <c r="C245" s="4"/>
@@ -6885,7 +6884,7 @@
       <c r="S245" s="8"/>
       <c r="T245" s="8"/>
     </row>
-    <row r="246" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" ht="20.25" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A246" s="12"/>
       <c r="B246" s="12"/>
       <c r="C246" s="4"/>
@@ -6907,7 +6906,7 @@
       <c r="S246" s="8"/>
       <c r="T246" s="8"/>
     </row>
-    <row r="247" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A247" s="12"/>
       <c r="B247" s="12"/>
       <c r="C247" s="4"/>
@@ -6929,7 +6928,7 @@
       <c r="S247" s="8"/>
       <c r="T247" s="8"/>
     </row>
-    <row r="248" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A248" s="12"/>
       <c r="B248" s="12"/>
       <c r="C248" s="4"/>
@@ -6951,7 +6950,7 @@
       <c r="S248" s="8"/>
       <c r="T248" s="8"/>
     </row>
-    <row r="249" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A249" s="12"/>
       <c r="B249" s="12"/>
       <c r="C249" s="4"/>
@@ -6973,7 +6972,7 @@
       <c r="S249" s="8"/>
       <c r="T249" s="8"/>
     </row>
-    <row r="250" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A250" s="12"/>
       <c r="B250" s="12"/>
       <c r="C250" s="4"/>
@@ -6995,7 +6994,7 @@
       <c r="S250" s="8"/>
       <c r="T250" s="8"/>
     </row>
-    <row r="251" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A251" s="12"/>
       <c r="B251" s="12"/>
       <c r="C251" s="4"/>
@@ -7017,7 +7016,7 @@
       <c r="S251" s="8"/>
       <c r="T251" s="8"/>
     </row>
-    <row r="252" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A252" s="12"/>
       <c r="B252" s="12"/>
       <c r="C252" s="4"/>
@@ -7039,7 +7038,7 @@
       <c r="S252" s="8"/>
       <c r="T252" s="8"/>
     </row>
-    <row r="253" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A253" s="12"/>
       <c r="B253" s="12"/>
       <c r="C253" s="4"/>
@@ -7061,7 +7060,7 @@
       <c r="S253" s="8"/>
       <c r="T253" s="8"/>
     </row>
-    <row r="254" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A254" s="12"/>
       <c r="B254" s="12"/>
       <c r="C254" s="4"/>
@@ -7083,7 +7082,7 @@
       <c r="S254" s="8"/>
       <c r="T254" s="8"/>
     </row>
-    <row r="255" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A255" s="12"/>
       <c r="B255" s="12"/>
       <c r="C255" s="4"/>
@@ -7105,7 +7104,7 @@
       <c r="S255" s="8"/>
       <c r="T255" s="8"/>
     </row>
-    <row r="256" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A256" s="12"/>
       <c r="B256" s="12"/>
       <c r="C256" s="4"/>
@@ -7127,7 +7126,7 @@
       <c r="S256" s="8"/>
       <c r="T256" s="8"/>
     </row>
-    <row r="257" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A257" s="12"/>
       <c r="B257" s="12"/>
       <c r="C257" s="4"/>
@@ -7149,7 +7148,7 @@
       <c r="S257" s="8"/>
       <c r="T257" s="8"/>
     </row>
-    <row r="258" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A258" s="12"/>
       <c r="B258" s="12"/>
       <c r="C258" s="4"/>
@@ -7171,7 +7170,7 @@
       <c r="S258" s="8"/>
       <c r="T258" s="8"/>
     </row>
-    <row r="259" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A259" s="12"/>
       <c r="B259" s="12"/>
       <c r="C259" s="4"/>
@@ -7193,7 +7192,7 @@
       <c r="S259" s="8"/>
       <c r="T259" s="8"/>
     </row>
-    <row r="260" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A260" s="12"/>
       <c r="B260" s="12"/>
       <c r="C260" s="4"/>
@@ -7215,7 +7214,7 @@
       <c r="S260" s="8"/>
       <c r="T260" s="8"/>
     </row>
-    <row r="261" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A261" s="12"/>
       <c r="B261" s="12"/>
       <c r="C261" s="4"/>
@@ -7237,7 +7236,7 @@
       <c r="S261" s="8"/>
       <c r="T261" s="8"/>
     </row>
-    <row r="262" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A262" s="12"/>
       <c r="B262" s="12"/>
       <c r="C262" s="4"/>
@@ -7259,7 +7258,7 @@
       <c r="S262" s="8"/>
       <c r="T262" s="8"/>
     </row>
-    <row r="263" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A263" s="12"/>
       <c r="B263" s="12"/>
       <c r="C263" s="4"/>
@@ -7281,7 +7280,7 @@
       <c r="S263" s="8"/>
       <c r="T263" s="8"/>
     </row>
-    <row r="264" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A264" s="12"/>
       <c r="B264" s="12"/>
       <c r="C264" s="4"/>
@@ -7303,7 +7302,7 @@
       <c r="S264" s="8"/>
       <c r="T264" s="8"/>
     </row>
-    <row r="265" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A265" s="12"/>
       <c r="B265" s="12"/>
       <c r="C265" s="4"/>
@@ -7325,7 +7324,7 @@
       <c r="S265" s="8"/>
       <c r="T265" s="8"/>
     </row>
-    <row r="266" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A266" s="12"/>
       <c r="B266" s="12"/>
       <c r="C266" s="4"/>
@@ -7347,7 +7346,7 @@
       <c r="S266" s="8"/>
       <c r="T266" s="8"/>
     </row>
-    <row r="267" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A267" s="12"/>
       <c r="B267" s="12"/>
       <c r="C267" s="4"/>
@@ -7369,7 +7368,7 @@
       <c r="S267" s="8"/>
       <c r="T267" s="8"/>
     </row>
-    <row r="268" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A268" s="12"/>
       <c r="B268" s="12"/>
       <c r="C268" s="4"/>
@@ -7391,7 +7390,7 @@
       <c r="S268" s="8"/>
       <c r="T268" s="8"/>
     </row>
-    <row r="269" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A269" s="12"/>
       <c r="B269" s="12"/>
       <c r="C269" s="4"/>
@@ -7415,14 +7414,14 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AF269"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="17.85546875" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
@@ -7438,7 +7437,7 @@
     <col min="18" max="32" width="17.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="15.75" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7512,7 +7511,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:32" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" ht="21" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>98</v>
       </c>
@@ -7586,7 +7585,7 @@
       <c r="AE2" s="10"/>
       <c r="AF2" s="10"/>
     </row>
-    <row r="3" spans="1:32" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="21" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>98</v>
       </c>
@@ -7660,7 +7659,7 @@
       <c r="AE3" s="10"/>
       <c r="AF3" s="10"/>
     </row>
-    <row r="4" spans="1:32" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="21" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>98</v>
       </c>
@@ -7734,7 +7733,7 @@
       <c r="AE4" s="10"/>
       <c r="AF4" s="10"/>
     </row>
-    <row r="5" spans="1:32" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="21" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>98</v>
       </c>
@@ -7808,7 +7807,7 @@
       <c r="AE5" s="10"/>
       <c r="AF5" s="10"/>
     </row>
-    <row r="6" spans="1:32" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="21" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>98</v>
       </c>
@@ -7882,7 +7881,7 @@
       <c r="AE6" s="10"/>
       <c r="AF6" s="10"/>
     </row>
-    <row r="7" spans="1:32" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="21" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>98</v>
       </c>
@@ -7956,7 +7955,7 @@
       <c r="AE7" s="10"/>
       <c r="AF7" s="10"/>
     </row>
-    <row r="8" spans="1:32" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="21" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>98</v>
       </c>
@@ -8030,7 +8029,7 @@
       <c r="AE8" s="10"/>
       <c r="AF8" s="10"/>
     </row>
-    <row r="9" spans="1:32" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="21" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>98</v>
       </c>
@@ -8104,7 +8103,7 @@
       <c r="AE9" s="10"/>
       <c r="AF9" s="10"/>
     </row>
-    <row r="10" spans="1:32" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" ht="21" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>98</v>
       </c>
@@ -8178,11 +8177,11 @@
       <c r="AE10" s="10"/>
       <c r="AF10" s="10"/>
     </row>
-    <row r="11" spans="1:32" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="20" t="s">
+    <row r="11" ht="21" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A11" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="B11" s="20"/>
+      <c r="B11" s="17"/>
       <c r="C11" s="4" t="s">
         <v>98</v>
       </c>
@@ -8191,17 +8190,17 @@
       <c r="F11" s="4"/>
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
-      <c r="I11" s="20" t="s">
+      <c r="I11" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="J11" s="20"/>
+      <c r="J11" s="17"/>
       <c r="K11" s="4"/>
       <c r="L11" s="6"/>
       <c r="M11" s="6"/>
       <c r="N11" s="6"/>
       <c r="O11" s="6"/>
       <c r="P11" s="6"/>
-      <c r="Q11" s="17" t="s">
+      <c r="Q11" s="18" t="s">
         <v>117</v>
       </c>
       <c r="R11" s="7"/>
@@ -8209,7 +8208,7 @@
       <c r="T11" s="4"/>
       <c r="U11" s="8"/>
       <c r="V11" s="8"/>
-      <c r="W11" s="18" t="s">
+      <c r="W11" s="19" t="s">
         <v>118</v>
       </c>
       <c r="X11" s="6"/>
@@ -8222,7 +8221,7 @@
       <c r="AE11" s="10"/>
       <c r="AF11" s="10"/>
     </row>
-    <row r="12" spans="1:32" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" ht="21" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -8256,7 +8255,7 @@
       <c r="AE12" s="10"/>
       <c r="AF12" s="10"/>
     </row>
-    <row r="13" spans="1:32" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" ht="21" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -8290,7 +8289,7 @@
       <c r="AE13" s="10"/>
       <c r="AF13" s="10"/>
     </row>
-    <row r="14" spans="1:32" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" ht="21" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
@@ -8324,7 +8323,7 @@
       <c r="AE14" s="10"/>
       <c r="AF14" s="10"/>
     </row>
-    <row r="15" spans="1:32" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" ht="21" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A15" s="4"/>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -8358,7 +8357,7 @@
       <c r="AE15" s="10"/>
       <c r="AF15" s="10"/>
     </row>
-    <row r="16" spans="1:32" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" ht="21" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A16" s="4"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
@@ -8392,7 +8391,7 @@
       <c r="AE16" s="10"/>
       <c r="AF16" s="10"/>
     </row>
-    <row r="17" spans="1:32" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" ht="21" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A17" s="4"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
@@ -8426,7 +8425,7 @@
       <c r="AE17" s="10"/>
       <c r="AF17" s="10"/>
     </row>
-    <row r="18" spans="1:32" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" ht="21" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A18" s="4"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
@@ -8460,7 +8459,7 @@
       <c r="AE18" s="10"/>
       <c r="AF18" s="10"/>
     </row>
-    <row r="19" spans="1:32" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" ht="21" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A19" s="4"/>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
@@ -8494,7 +8493,7 @@
       <c r="AE19" s="10"/>
       <c r="AF19" s="10"/>
     </row>
-    <row r="20" spans="1:32" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" ht="21" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A20" s="4"/>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
@@ -8528,7 +8527,7 @@
       <c r="AE20" s="10"/>
       <c r="AF20" s="10"/>
     </row>
-    <row r="21" spans="1:32" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" ht="21" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A21" s="4"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
@@ -8562,7 +8561,7 @@
       <c r="AE21" s="10"/>
       <c r="AF21" s="10"/>
     </row>
-    <row r="22" spans="1:32" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" ht="21" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A22" s="4"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -8596,7 +8595,7 @@
       <c r="AE22" s="10"/>
       <c r="AF22" s="10"/>
     </row>
-    <row r="23" spans="1:32" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" ht="21" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -8630,7 +8629,7 @@
       <c r="AE23" s="10"/>
       <c r="AF23" s="10"/>
     </row>
-    <row r="24" spans="1:32" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" ht="21" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A24" s="4"/>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
@@ -8664,7 +8663,7 @@
       <c r="AE24" s="10"/>
       <c r="AF24" s="10"/>
     </row>
-    <row r="25" spans="1:32" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" ht="21" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" s="12"/>
       <c r="B25" s="12"/>
       <c r="C25" s="4"/>
@@ -8690,7 +8689,7 @@
       <c r="W25" s="8"/>
       <c r="X25" s="13"/>
     </row>
-    <row r="26" spans="1:32" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" ht="21" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" s="12"/>
       <c r="B26" s="12"/>
       <c r="C26" s="4"/>
@@ -8716,7 +8715,7 @@
       <c r="W26" s="8"/>
       <c r="X26" s="14"/>
     </row>
-    <row r="27" spans="1:32" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A27" s="12"/>
       <c r="B27" s="12"/>
       <c r="C27" s="4"/>
@@ -8741,7 +8740,7 @@
       <c r="V27" s="8"/>
       <c r="W27" s="8"/>
     </row>
-    <row r="28" spans="1:32" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A28" s="12"/>
       <c r="B28" s="12"/>
       <c r="C28" s="4"/>
@@ -8766,7 +8765,7 @@
       <c r="V28" s="8"/>
       <c r="W28" s="8"/>
     </row>
-    <row r="29" spans="1:32" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A29" s="12"/>
       <c r="B29" s="12"/>
       <c r="C29" s="4"/>
@@ -8791,7 +8790,7 @@
       <c r="V29" s="8"/>
       <c r="W29" s="8"/>
     </row>
-    <row r="30" spans="1:32" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A30" s="12"/>
       <c r="B30" s="12"/>
       <c r="C30" s="4"/>
@@ -8816,7 +8815,7 @@
       <c r="V30" s="8"/>
       <c r="W30" s="8"/>
     </row>
-    <row r="31" spans="1:32" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" ht="21" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31" s="12"/>
       <c r="B31" s="12"/>
       <c r="C31" s="4"/>
@@ -8842,7 +8841,7 @@
       <c r="W31" s="8"/>
       <c r="X31" s="13"/>
     </row>
-    <row r="32" spans="1:32" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" ht="21" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A32" s="12"/>
       <c r="B32" s="12"/>
       <c r="C32" s="4"/>
@@ -8868,7 +8867,7 @@
       <c r="W32" s="8"/>
       <c r="X32" s="13"/>
     </row>
-    <row r="33" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" ht="21" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A33" s="12"/>
       <c r="B33" s="12"/>
       <c r="C33" s="4"/>
@@ -8894,7 +8893,7 @@
       <c r="W33" s="8"/>
       <c r="X33" s="13"/>
     </row>
-    <row r="34" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" ht="21" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A34" s="12"/>
       <c r="B34" s="12"/>
       <c r="C34" s="4"/>
@@ -8920,7 +8919,7 @@
       <c r="W34" s="8"/>
       <c r="X34" s="13"/>
     </row>
-    <row r="35" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A35" s="12"/>
       <c r="B35" s="12"/>
       <c r="C35" s="4"/>
@@ -8945,7 +8944,7 @@
       <c r="V35" s="8"/>
       <c r="W35" s="8"/>
     </row>
-    <row r="36" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" ht="21" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A36" s="12"/>
       <c r="B36" s="12"/>
       <c r="C36" s="4"/>
@@ -8971,7 +8970,7 @@
       <c r="W36" s="8"/>
       <c r="X36" s="14"/>
     </row>
-    <row r="37" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A37" s="12"/>
       <c r="B37" s="12"/>
       <c r="C37" s="4"/>
@@ -8996,7 +8995,7 @@
       <c r="V37" s="8"/>
       <c r="W37" s="8"/>
     </row>
-    <row r="38" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A38" s="12"/>
       <c r="B38" s="12"/>
       <c r="C38" s="4"/>
@@ -9021,7 +9020,7 @@
       <c r="V38" s="8"/>
       <c r="W38" s="8"/>
     </row>
-    <row r="39" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" ht="21" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A39" s="12"/>
       <c r="B39" s="12"/>
       <c r="C39" s="4"/>
@@ -9047,7 +9046,7 @@
       <c r="W39" s="8"/>
       <c r="X39" s="13"/>
     </row>
-    <row r="40" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" ht="21" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A40" s="12"/>
       <c r="B40" s="12"/>
       <c r="C40" s="4"/>
@@ -9073,7 +9072,7 @@
       <c r="W40" s="8"/>
       <c r="X40" s="13"/>
     </row>
-    <row r="41" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A41" s="12"/>
       <c r="B41" s="12"/>
       <c r="C41" s="4"/>
@@ -9098,7 +9097,7 @@
       <c r="V41" s="8"/>
       <c r="W41" s="8"/>
     </row>
-    <row r="42" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A42" s="12"/>
       <c r="B42" s="12"/>
       <c r="C42" s="4"/>
@@ -9123,7 +9122,7 @@
       <c r="V42" s="8"/>
       <c r="W42" s="8"/>
     </row>
-    <row r="43" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" ht="21" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A43" s="12"/>
       <c r="B43" s="12"/>
       <c r="C43" s="4"/>
@@ -9149,7 +9148,7 @@
       <c r="W43" s="8"/>
       <c r="X43" s="14"/>
     </row>
-    <row r="44" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A44" s="12"/>
       <c r="B44" s="12"/>
       <c r="C44" s="4"/>
@@ -9174,7 +9173,7 @@
       <c r="V44" s="8"/>
       <c r="W44" s="8"/>
     </row>
-    <row r="45" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" ht="21" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A45" s="12"/>
       <c r="B45" s="12"/>
       <c r="C45" s="4"/>
@@ -9200,7 +9199,7 @@
       <c r="W45" s="8"/>
       <c r="X45" s="14"/>
     </row>
-    <row r="46" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A46" s="12"/>
       <c r="B46" s="12"/>
       <c r="C46" s="4"/>
@@ -9225,7 +9224,7 @@
       <c r="V46" s="8"/>
       <c r="W46" s="8"/>
     </row>
-    <row r="47" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A47" s="12"/>
       <c r="B47" s="12"/>
       <c r="C47" s="4"/>
@@ -9250,7 +9249,7 @@
       <c r="V47" s="8"/>
       <c r="W47" s="8"/>
     </row>
-    <row r="48" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A48" s="12"/>
       <c r="B48" s="12"/>
       <c r="C48" s="4"/>
@@ -9275,7 +9274,7 @@
       <c r="V48" s="8"/>
       <c r="W48" s="8"/>
     </row>
-    <row r="49" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A49" s="12"/>
       <c r="B49" s="12"/>
       <c r="C49" s="4"/>
@@ -9300,7 +9299,7 @@
       <c r="V49" s="8"/>
       <c r="W49" s="8"/>
     </row>
-    <row r="50" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A50" s="12"/>
       <c r="B50" s="12"/>
       <c r="C50" s="4"/>
@@ -9325,7 +9324,7 @@
       <c r="V50" s="8"/>
       <c r="W50" s="8"/>
     </row>
-    <row r="51" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A51" s="12"/>
       <c r="B51" s="12"/>
       <c r="C51" s="4"/>
@@ -9350,7 +9349,7 @@
       <c r="V51" s="8"/>
       <c r="W51" s="8"/>
     </row>
-    <row r="52" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A52" s="12"/>
       <c r="B52" s="12"/>
       <c r="C52" s="4"/>
@@ -9375,7 +9374,7 @@
       <c r="V52" s="8"/>
       <c r="W52" s="8"/>
     </row>
-    <row r="53" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A53" s="12"/>
       <c r="B53" s="12"/>
       <c r="C53" s="4"/>
@@ -9400,7 +9399,7 @@
       <c r="V53" s="8"/>
       <c r="W53" s="8"/>
     </row>
-    <row r="54" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A54" s="12"/>
       <c r="B54" s="12"/>
       <c r="C54" s="4"/>
@@ -9425,7 +9424,7 @@
       <c r="V54" s="8"/>
       <c r="W54" s="8"/>
     </row>
-    <row r="55" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A55" s="12"/>
       <c r="B55" s="12"/>
       <c r="C55" s="4"/>
@@ -9450,7 +9449,7 @@
       <c r="V55" s="8"/>
       <c r="W55" s="8"/>
     </row>
-    <row r="56" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A56" s="12"/>
       <c r="B56" s="12"/>
       <c r="C56" s="4"/>
@@ -9475,7 +9474,7 @@
       <c r="V56" s="8"/>
       <c r="W56" s="8"/>
     </row>
-    <row r="57" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A57" s="12"/>
       <c r="B57" s="12"/>
       <c r="C57" s="4"/>
@@ -9500,7 +9499,7 @@
       <c r="V57" s="8"/>
       <c r="W57" s="8"/>
     </row>
-    <row r="58" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A58" s="12"/>
       <c r="B58" s="12"/>
       <c r="C58" s="4"/>
@@ -9525,7 +9524,7 @@
       <c r="V58" s="8"/>
       <c r="W58" s="8"/>
     </row>
-    <row r="59" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A59" s="12"/>
       <c r="B59" s="12"/>
       <c r="C59" s="4"/>
@@ -9550,7 +9549,7 @@
       <c r="V59" s="8"/>
       <c r="W59" s="8"/>
     </row>
-    <row r="60" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A60" s="12"/>
       <c r="B60" s="12"/>
       <c r="C60" s="4"/>
@@ -9575,7 +9574,7 @@
       <c r="V60" s="8"/>
       <c r="W60" s="8"/>
     </row>
-    <row r="61" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A61" s="12"/>
       <c r="B61" s="12"/>
       <c r="C61" s="4"/>
@@ -9600,7 +9599,7 @@
       <c r="V61" s="8"/>
       <c r="W61" s="8"/>
     </row>
-    <row r="62" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A62" s="12"/>
       <c r="B62" s="12"/>
       <c r="C62" s="4"/>
@@ -9625,7 +9624,7 @@
       <c r="V62" s="8"/>
       <c r="W62" s="8"/>
     </row>
-    <row r="63" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A63" s="12"/>
       <c r="B63" s="12"/>
       <c r="C63" s="4"/>
@@ -9650,7 +9649,7 @@
       <c r="V63" s="8"/>
       <c r="W63" s="8"/>
     </row>
-    <row r="64" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A64" s="12"/>
       <c r="B64" s="12"/>
       <c r="C64" s="4"/>
@@ -9675,7 +9674,7 @@
       <c r="V64" s="8"/>
       <c r="W64" s="8"/>
     </row>
-    <row r="65" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A65" s="12"/>
       <c r="B65" s="12"/>
       <c r="C65" s="4"/>
@@ -9700,7 +9699,7 @@
       <c r="V65" s="8"/>
       <c r="W65" s="8"/>
     </row>
-    <row r="66" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A66" s="12"/>
       <c r="B66" s="12"/>
       <c r="C66" s="4"/>
@@ -9725,7 +9724,7 @@
       <c r="V66" s="8"/>
       <c r="W66" s="8"/>
     </row>
-    <row r="67" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A67" s="12"/>
       <c r="B67" s="12"/>
       <c r="C67" s="4"/>
@@ -9750,7 +9749,7 @@
       <c r="V67" s="8"/>
       <c r="W67" s="8"/>
     </row>
-    <row r="68" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A68" s="12"/>
       <c r="B68" s="12"/>
       <c r="C68" s="4"/>
@@ -9775,7 +9774,7 @@
       <c r="V68" s="8"/>
       <c r="W68" s="8"/>
     </row>
-    <row r="69" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A69" s="12"/>
       <c r="B69" s="12"/>
       <c r="C69" s="4"/>
@@ -9800,7 +9799,7 @@
       <c r="V69" s="8"/>
       <c r="W69" s="8"/>
     </row>
-    <row r="70" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A70" s="12"/>
       <c r="B70" s="12"/>
       <c r="C70" s="4"/>
@@ -9825,7 +9824,7 @@
       <c r="V70" s="8"/>
       <c r="W70" s="8"/>
     </row>
-    <row r="71" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A71" s="12"/>
       <c r="B71" s="12"/>
       <c r="C71" s="4"/>
@@ -9850,7 +9849,7 @@
       <c r="V71" s="8"/>
       <c r="W71" s="8"/>
     </row>
-    <row r="72" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A72" s="12"/>
       <c r="B72" s="12"/>
       <c r="C72" s="4"/>
@@ -9875,7 +9874,7 @@
       <c r="V72" s="8"/>
       <c r="W72" s="8"/>
     </row>
-    <row r="73" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A73" s="12"/>
       <c r="B73" s="12"/>
       <c r="C73" s="4"/>
@@ -9900,7 +9899,7 @@
       <c r="V73" s="8"/>
       <c r="W73" s="8"/>
     </row>
-    <row r="74" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A74" s="12"/>
       <c r="B74" s="12"/>
       <c r="C74" s="4"/>
@@ -9925,7 +9924,7 @@
       <c r="V74" s="8"/>
       <c r="W74" s="8"/>
     </row>
-    <row r="75" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A75" s="12"/>
       <c r="B75" s="12"/>
       <c r="C75" s="4"/>
@@ -9950,7 +9949,7 @@
       <c r="V75" s="8"/>
       <c r="W75" s="8"/>
     </row>
-    <row r="76" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A76" s="12"/>
       <c r="B76" s="12"/>
       <c r="C76" s="4"/>
@@ -9975,7 +9974,7 @@
       <c r="V76" s="8"/>
       <c r="W76" s="8"/>
     </row>
-    <row r="77" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A77" s="12"/>
       <c r="B77" s="12"/>
       <c r="C77" s="4"/>
@@ -10000,7 +9999,7 @@
       <c r="V77" s="8"/>
       <c r="W77" s="8"/>
     </row>
-    <row r="78" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A78" s="12"/>
       <c r="B78" s="12"/>
       <c r="C78" s="4"/>
@@ -10025,7 +10024,7 @@
       <c r="V78" s="8"/>
       <c r="W78" s="8"/>
     </row>
-    <row r="79" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A79" s="12"/>
       <c r="B79" s="12"/>
       <c r="C79" s="4"/>
@@ -10050,7 +10049,7 @@
       <c r="V79" s="8"/>
       <c r="W79" s="8"/>
     </row>
-    <row r="80" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A80" s="12"/>
       <c r="B80" s="12"/>
       <c r="C80" s="4"/>
@@ -10075,7 +10074,7 @@
       <c r="V80" s="8"/>
       <c r="W80" s="8"/>
     </row>
-    <row r="81" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A81" s="12"/>
       <c r="B81" s="12"/>
       <c r="C81" s="4"/>
@@ -10100,7 +10099,7 @@
       <c r="V81" s="8"/>
       <c r="W81" s="8"/>
     </row>
-    <row r="82" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A82" s="12"/>
       <c r="B82" s="12"/>
       <c r="C82" s="4"/>
@@ -10125,7 +10124,7 @@
       <c r="V82" s="8"/>
       <c r="W82" s="8"/>
     </row>
-    <row r="83" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A83" s="12"/>
       <c r="B83" s="12"/>
       <c r="C83" s="4"/>
@@ -10150,7 +10149,7 @@
       <c r="V83" s="8"/>
       <c r="W83" s="8"/>
     </row>
-    <row r="84" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A84" s="12"/>
       <c r="B84" s="12"/>
       <c r="C84" s="4"/>
@@ -10175,7 +10174,7 @@
       <c r="V84" s="8"/>
       <c r="W84" s="8"/>
     </row>
-    <row r="85" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A85" s="12"/>
       <c r="B85" s="12"/>
       <c r="C85" s="4"/>
@@ -10200,7 +10199,7 @@
       <c r="V85" s="8"/>
       <c r="W85" s="8"/>
     </row>
-    <row r="86" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A86" s="12"/>
       <c r="B86" s="12"/>
       <c r="C86" s="4"/>
@@ -10225,7 +10224,7 @@
       <c r="V86" s="8"/>
       <c r="W86" s="8"/>
     </row>
-    <row r="87" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A87" s="12"/>
       <c r="B87" s="12"/>
       <c r="C87" s="4"/>
@@ -10250,7 +10249,7 @@
       <c r="V87" s="8"/>
       <c r="W87" s="8"/>
     </row>
-    <row r="88" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A88" s="12"/>
       <c r="B88" s="12"/>
       <c r="C88" s="4"/>
@@ -10275,7 +10274,7 @@
       <c r="V88" s="8"/>
       <c r="W88" s="8"/>
     </row>
-    <row r="89" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A89" s="12"/>
       <c r="B89" s="12"/>
       <c r="C89" s="4"/>
@@ -10300,7 +10299,7 @@
       <c r="V89" s="8"/>
       <c r="W89" s="8"/>
     </row>
-    <row r="90" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A90" s="12"/>
       <c r="B90" s="12"/>
       <c r="C90" s="4"/>
@@ -10325,7 +10324,7 @@
       <c r="V90" s="8"/>
       <c r="W90" s="8"/>
     </row>
-    <row r="91" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A91" s="12"/>
       <c r="B91" s="12"/>
       <c r="C91" s="4"/>
@@ -10350,7 +10349,7 @@
       <c r="V91" s="8"/>
       <c r="W91" s="8"/>
     </row>
-    <row r="92" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A92" s="12"/>
       <c r="B92" s="12"/>
       <c r="C92" s="4"/>
@@ -10375,7 +10374,7 @@
       <c r="V92" s="8"/>
       <c r="W92" s="8"/>
     </row>
-    <row r="93" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A93" s="12"/>
       <c r="B93" s="12"/>
       <c r="C93" s="4"/>
@@ -10400,7 +10399,7 @@
       <c r="V93" s="8"/>
       <c r="W93" s="8"/>
     </row>
-    <row r="94" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A94" s="12"/>
       <c r="B94" s="12"/>
       <c r="C94" s="4"/>
@@ -10425,7 +10424,7 @@
       <c r="V94" s="8"/>
       <c r="W94" s="8"/>
     </row>
-    <row r="95" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A95" s="12"/>
       <c r="B95" s="12"/>
       <c r="C95" s="4"/>
@@ -10450,7 +10449,7 @@
       <c r="V95" s="8"/>
       <c r="W95" s="8"/>
     </row>
-    <row r="96" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A96" s="12"/>
       <c r="B96" s="12"/>
       <c r="C96" s="4"/>
@@ -10475,7 +10474,7 @@
       <c r="V96" s="8"/>
       <c r="W96" s="8"/>
     </row>
-    <row r="97" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A97" s="12"/>
       <c r="B97" s="12"/>
       <c r="C97" s="4"/>
@@ -10500,7 +10499,7 @@
       <c r="V97" s="8"/>
       <c r="W97" s="8"/>
     </row>
-    <row r="98" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A98" s="12"/>
       <c r="B98" s="12"/>
       <c r="C98" s="4"/>
@@ -10525,7 +10524,7 @@
       <c r="V98" s="8"/>
       <c r="W98" s="8"/>
     </row>
-    <row r="99" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A99" s="12"/>
       <c r="B99" s="12"/>
       <c r="C99" s="4"/>
@@ -10550,7 +10549,7 @@
       <c r="V99" s="8"/>
       <c r="W99" s="8"/>
     </row>
-    <row r="100" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A100" s="12"/>
       <c r="B100" s="12"/>
       <c r="C100" s="4"/>
@@ -10575,7 +10574,7 @@
       <c r="V100" s="8"/>
       <c r="W100" s="8"/>
     </row>
-    <row r="101" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A101" s="12"/>
       <c r="B101" s="12"/>
       <c r="C101" s="4"/>
@@ -10600,7 +10599,7 @@
       <c r="V101" s="8"/>
       <c r="W101" s="8"/>
     </row>
-    <row r="102" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A102" s="12"/>
       <c r="B102" s="12"/>
       <c r="C102" s="4"/>
@@ -10625,7 +10624,7 @@
       <c r="V102" s="8"/>
       <c r="W102" s="8"/>
     </row>
-    <row r="103" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A103" s="12"/>
       <c r="B103" s="12"/>
       <c r="C103" s="4"/>
@@ -10650,7 +10649,7 @@
       <c r="V103" s="8"/>
       <c r="W103" s="8"/>
     </row>
-    <row r="104" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A104" s="12"/>
       <c r="B104" s="12"/>
       <c r="C104" s="4"/>
@@ -10675,7 +10674,7 @@
       <c r="V104" s="8"/>
       <c r="W104" s="8"/>
     </row>
-    <row r="105" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A105" s="12"/>
       <c r="B105" s="12"/>
       <c r="C105" s="4"/>
@@ -10700,7 +10699,7 @@
       <c r="V105" s="8"/>
       <c r="W105" s="8"/>
     </row>
-    <row r="106" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A106" s="12"/>
       <c r="B106" s="12"/>
       <c r="C106" s="4"/>
@@ -10725,7 +10724,7 @@
       <c r="V106" s="8"/>
       <c r="W106" s="8"/>
     </row>
-    <row r="107" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A107" s="12"/>
       <c r="B107" s="12"/>
       <c r="C107" s="4"/>
@@ -10750,7 +10749,7 @@
       <c r="V107" s="8"/>
       <c r="W107" s="8"/>
     </row>
-    <row r="108" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A108" s="12"/>
       <c r="B108" s="12"/>
       <c r="C108" s="4"/>
@@ -10775,7 +10774,7 @@
       <c r="V108" s="8"/>
       <c r="W108" s="8"/>
     </row>
-    <row r="109" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A109" s="12"/>
       <c r="B109" s="12"/>
       <c r="C109" s="4"/>
@@ -10800,7 +10799,7 @@
       <c r="V109" s="8"/>
       <c r="W109" s="8"/>
     </row>
-    <row r="110" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A110" s="12"/>
       <c r="B110" s="12"/>
       <c r="C110" s="4"/>
@@ -10825,7 +10824,7 @@
       <c r="V110" s="8"/>
       <c r="W110" s="8"/>
     </row>
-    <row r="111" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A111" s="12"/>
       <c r="B111" s="12"/>
       <c r="C111" s="4"/>
@@ -10850,7 +10849,7 @@
       <c r="V111" s="8"/>
       <c r="W111" s="8"/>
     </row>
-    <row r="112" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A112" s="12"/>
       <c r="B112" s="12"/>
       <c r="C112" s="4"/>
@@ -10875,7 +10874,7 @@
       <c r="V112" s="8"/>
       <c r="W112" s="8"/>
     </row>
-    <row r="113" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A113" s="12"/>
       <c r="B113" s="12"/>
       <c r="C113" s="4"/>
@@ -10900,7 +10899,7 @@
       <c r="V113" s="8"/>
       <c r="W113" s="8"/>
     </row>
-    <row r="114" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A114" s="12"/>
       <c r="B114" s="12"/>
       <c r="C114" s="4"/>
@@ -10925,7 +10924,7 @@
       <c r="V114" s="8"/>
       <c r="W114" s="8"/>
     </row>
-    <row r="115" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A115" s="12"/>
       <c r="B115" s="12"/>
       <c r="C115" s="4"/>
@@ -10950,7 +10949,7 @@
       <c r="V115" s="8"/>
       <c r="W115" s="8"/>
     </row>
-    <row r="116" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A116" s="12"/>
       <c r="B116" s="12"/>
       <c r="C116" s="4"/>
@@ -10975,7 +10974,7 @@
       <c r="V116" s="8"/>
       <c r="W116" s="8"/>
     </row>
-    <row r="117" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A117" s="12"/>
       <c r="B117" s="12"/>
       <c r="C117" s="4"/>
@@ -11000,7 +10999,7 @@
       <c r="V117" s="8"/>
       <c r="W117" s="8"/>
     </row>
-    <row r="118" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A118" s="12"/>
       <c r="B118" s="12"/>
       <c r="C118" s="4"/>
@@ -11025,7 +11024,7 @@
       <c r="V118" s="8"/>
       <c r="W118" s="8"/>
     </row>
-    <row r="119" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A119" s="12"/>
       <c r="B119" s="12"/>
       <c r="C119" s="4"/>
@@ -11050,7 +11049,7 @@
       <c r="V119" s="8"/>
       <c r="W119" s="8"/>
     </row>
-    <row r="120" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A120" s="12"/>
       <c r="B120" s="12"/>
       <c r="C120" s="4"/>
@@ -11075,7 +11074,7 @@
       <c r="V120" s="8"/>
       <c r="W120" s="8"/>
     </row>
-    <row r="121" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A121" s="12"/>
       <c r="B121" s="12"/>
       <c r="C121" s="4"/>
@@ -11100,7 +11099,7 @@
       <c r="V121" s="8"/>
       <c r="W121" s="8"/>
     </row>
-    <row r="122" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A122" s="12"/>
       <c r="B122" s="12"/>
       <c r="C122" s="4"/>
@@ -11125,7 +11124,7 @@
       <c r="V122" s="8"/>
       <c r="W122" s="8"/>
     </row>
-    <row r="123" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A123" s="12"/>
       <c r="B123" s="12"/>
       <c r="C123" s="4"/>
@@ -11150,7 +11149,7 @@
       <c r="V123" s="8"/>
       <c r="W123" s="8"/>
     </row>
-    <row r="124" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A124" s="12"/>
       <c r="B124" s="12"/>
       <c r="C124" s="4"/>
@@ -11175,7 +11174,7 @@
       <c r="V124" s="8"/>
       <c r="W124" s="8"/>
     </row>
-    <row r="125" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A125" s="12"/>
       <c r="B125" s="12"/>
       <c r="C125" s="4"/>
@@ -11200,7 +11199,7 @@
       <c r="V125" s="8"/>
       <c r="W125" s="8"/>
     </row>
-    <row r="126" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A126" s="12"/>
       <c r="B126" s="12"/>
       <c r="C126" s="4"/>
@@ -11225,7 +11224,7 @@
       <c r="V126" s="8"/>
       <c r="W126" s="8"/>
     </row>
-    <row r="127" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A127" s="12"/>
       <c r="B127" s="12"/>
       <c r="C127" s="4"/>
@@ -11250,7 +11249,7 @@
       <c r="V127" s="8"/>
       <c r="W127" s="8"/>
     </row>
-    <row r="128" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A128" s="12"/>
       <c r="B128" s="12"/>
       <c r="C128" s="4"/>
@@ -11275,7 +11274,7 @@
       <c r="V128" s="8"/>
       <c r="W128" s="8"/>
     </row>
-    <row r="129" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A129" s="12"/>
       <c r="B129" s="12"/>
       <c r="C129" s="4"/>
@@ -11300,7 +11299,7 @@
       <c r="V129" s="8"/>
       <c r="W129" s="8"/>
     </row>
-    <row r="130" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A130" s="12"/>
       <c r="B130" s="12"/>
       <c r="C130" s="4"/>
@@ -11325,7 +11324,7 @@
       <c r="V130" s="8"/>
       <c r="W130" s="8"/>
     </row>
-    <row r="131" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A131" s="12"/>
       <c r="B131" s="12"/>
       <c r="C131" s="4"/>
@@ -11350,7 +11349,7 @@
       <c r="V131" s="8"/>
       <c r="W131" s="8"/>
     </row>
-    <row r="132" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A132" s="12"/>
       <c r="B132" s="12"/>
       <c r="C132" s="4"/>
@@ -11375,7 +11374,7 @@
       <c r="V132" s="8"/>
       <c r="W132" s="8"/>
     </row>
-    <row r="133" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A133" s="12"/>
       <c r="B133" s="12"/>
       <c r="C133" s="4"/>
@@ -11400,7 +11399,7 @@
       <c r="V133" s="8"/>
       <c r="W133" s="8"/>
     </row>
-    <row r="134" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A134" s="12"/>
       <c r="B134" s="12"/>
       <c r="C134" s="4"/>
@@ -11425,7 +11424,7 @@
       <c r="V134" s="8"/>
       <c r="W134" s="8"/>
     </row>
-    <row r="135" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A135" s="12"/>
       <c r="B135" s="12"/>
       <c r="C135" s="4"/>
@@ -11450,7 +11449,7 @@
       <c r="V135" s="8"/>
       <c r="W135" s="8"/>
     </row>
-    <row r="136" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A136" s="12"/>
       <c r="B136" s="12"/>
       <c r="C136" s="4"/>
@@ -11475,7 +11474,7 @@
       <c r="V136" s="8"/>
       <c r="W136" s="8"/>
     </row>
-    <row r="137" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A137" s="12"/>
       <c r="B137" s="12"/>
       <c r="C137" s="4"/>
@@ -11500,7 +11499,7 @@
       <c r="V137" s="8"/>
       <c r="W137" s="8"/>
     </row>
-    <row r="138" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A138" s="12"/>
       <c r="B138" s="12"/>
       <c r="C138" s="4"/>
@@ -11525,7 +11524,7 @@
       <c r="V138" s="8"/>
       <c r="W138" s="8"/>
     </row>
-    <row r="139" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A139" s="12"/>
       <c r="B139" s="12"/>
       <c r="C139" s="4"/>
@@ -11550,7 +11549,7 @@
       <c r="V139" s="8"/>
       <c r="W139" s="8"/>
     </row>
-    <row r="140" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A140" s="12"/>
       <c r="B140" s="12"/>
       <c r="C140" s="4"/>
@@ -11575,7 +11574,7 @@
       <c r="V140" s="8"/>
       <c r="W140" s="8"/>
     </row>
-    <row r="141" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A141" s="12"/>
       <c r="B141" s="12"/>
       <c r="C141" s="4"/>
@@ -11600,7 +11599,7 @@
       <c r="V141" s="8"/>
       <c r="W141" s="8"/>
     </row>
-    <row r="142" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A142" s="12"/>
       <c r="B142" s="12"/>
       <c r="C142" s="4"/>
@@ -11625,7 +11624,7 @@
       <c r="V142" s="8"/>
       <c r="W142" s="8"/>
     </row>
-    <row r="143" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A143" s="12"/>
       <c r="B143" s="12"/>
       <c r="C143" s="4"/>
@@ -11650,7 +11649,7 @@
       <c r="V143" s="8"/>
       <c r="W143" s="8"/>
     </row>
-    <row r="144" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A144" s="12"/>
       <c r="B144" s="12"/>
       <c r="C144" s="4"/>
@@ -11675,7 +11674,7 @@
       <c r="V144" s="8"/>
       <c r="W144" s="8"/>
     </row>
-    <row r="145" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A145" s="12"/>
       <c r="B145" s="12"/>
       <c r="C145" s="4"/>
@@ -11700,7 +11699,7 @@
       <c r="V145" s="8"/>
       <c r="W145" s="8"/>
     </row>
-    <row r="146" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A146" s="12"/>
       <c r="B146" s="12"/>
       <c r="C146" s="4"/>
@@ -11725,7 +11724,7 @@
       <c r="V146" s="8"/>
       <c r="W146" s="8"/>
     </row>
-    <row r="147" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A147" s="12"/>
       <c r="B147" s="12"/>
       <c r="C147" s="4"/>
@@ -11750,7 +11749,7 @@
       <c r="V147" s="8"/>
       <c r="W147" s="8"/>
     </row>
-    <row r="148" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A148" s="12"/>
       <c r="B148" s="12"/>
       <c r="C148" s="4"/>
@@ -11775,7 +11774,7 @@
       <c r="V148" s="8"/>
       <c r="W148" s="8"/>
     </row>
-    <row r="149" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A149" s="12"/>
       <c r="B149" s="12"/>
       <c r="C149" s="4"/>
@@ -11800,7 +11799,7 @@
       <c r="V149" s="8"/>
       <c r="W149" s="8"/>
     </row>
-    <row r="150" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A150" s="12"/>
       <c r="B150" s="12"/>
       <c r="C150" s="4"/>
@@ -11825,7 +11824,7 @@
       <c r="V150" s="8"/>
       <c r="W150" s="8"/>
     </row>
-    <row r="151" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A151" s="12"/>
       <c r="B151" s="12"/>
       <c r="C151" s="4"/>
@@ -11850,7 +11849,7 @@
       <c r="V151" s="8"/>
       <c r="W151" s="8"/>
     </row>
-    <row r="152" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A152" s="12"/>
       <c r="B152" s="12"/>
       <c r="C152" s="4"/>
@@ -11875,7 +11874,7 @@
       <c r="V152" s="8"/>
       <c r="W152" s="8"/>
     </row>
-    <row r="153" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A153" s="12"/>
       <c r="B153" s="12"/>
       <c r="C153" s="4"/>
@@ -11900,7 +11899,7 @@
       <c r="V153" s="8"/>
       <c r="W153" s="8"/>
     </row>
-    <row r="154" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A154" s="12"/>
       <c r="B154" s="12"/>
       <c r="C154" s="4"/>
@@ -11925,7 +11924,7 @@
       <c r="V154" s="8"/>
       <c r="W154" s="8"/>
     </row>
-    <row r="155" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A155" s="12"/>
       <c r="B155" s="12"/>
       <c r="C155" s="4"/>
@@ -11950,7 +11949,7 @@
       <c r="V155" s="8"/>
       <c r="W155" s="8"/>
     </row>
-    <row r="156" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A156" s="12"/>
       <c r="B156" s="12"/>
       <c r="C156" s="4"/>
@@ -11975,7 +11974,7 @@
       <c r="V156" s="8"/>
       <c r="W156" s="8"/>
     </row>
-    <row r="157" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A157" s="12"/>
       <c r="B157" s="12"/>
       <c r="C157" s="4"/>
@@ -12000,7 +11999,7 @@
       <c r="V157" s="8"/>
       <c r="W157" s="8"/>
     </row>
-    <row r="158" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A158" s="12"/>
       <c r="B158" s="12"/>
       <c r="C158" s="4"/>
@@ -12025,7 +12024,7 @@
       <c r="V158" s="8"/>
       <c r="W158" s="8"/>
     </row>
-    <row r="159" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A159" s="12"/>
       <c r="B159" s="12"/>
       <c r="C159" s="4"/>
@@ -12050,7 +12049,7 @@
       <c r="V159" s="8"/>
       <c r="W159" s="8"/>
     </row>
-    <row r="160" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A160" s="12"/>
       <c r="B160" s="12"/>
       <c r="C160" s="4"/>
@@ -12075,7 +12074,7 @@
       <c r="V160" s="8"/>
       <c r="W160" s="8"/>
     </row>
-    <row r="161" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A161" s="12"/>
       <c r="B161" s="12"/>
       <c r="C161" s="4"/>
@@ -12100,7 +12099,7 @@
       <c r="V161" s="8"/>
       <c r="W161" s="8"/>
     </row>
-    <row r="162" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A162" s="12"/>
       <c r="B162" s="12"/>
       <c r="C162" s="4"/>
@@ -12125,7 +12124,7 @@
       <c r="V162" s="8"/>
       <c r="W162" s="8"/>
     </row>
-    <row r="163" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A163" s="12"/>
       <c r="B163" s="12"/>
       <c r="C163" s="4"/>
@@ -12150,7 +12149,7 @@
       <c r="V163" s="8"/>
       <c r="W163" s="8"/>
     </row>
-    <row r="164" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A164" s="12"/>
       <c r="B164" s="12"/>
       <c r="C164" s="4"/>
@@ -12175,7 +12174,7 @@
       <c r="V164" s="8"/>
       <c r="W164" s="8"/>
     </row>
-    <row r="165" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A165" s="12"/>
       <c r="B165" s="12"/>
       <c r="C165" s="4"/>
@@ -12200,7 +12199,7 @@
       <c r="V165" s="8"/>
       <c r="W165" s="8"/>
     </row>
-    <row r="166" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A166" s="12"/>
       <c r="B166" s="12"/>
       <c r="C166" s="4"/>
@@ -12225,7 +12224,7 @@
       <c r="V166" s="8"/>
       <c r="W166" s="8"/>
     </row>
-    <row r="167" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A167" s="12"/>
       <c r="B167" s="12"/>
       <c r="C167" s="4"/>
@@ -12250,7 +12249,7 @@
       <c r="V167" s="8"/>
       <c r="W167" s="8"/>
     </row>
-    <row r="168" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A168" s="12"/>
       <c r="B168" s="12"/>
       <c r="C168" s="4"/>
@@ -12275,7 +12274,7 @@
       <c r="V168" s="8"/>
       <c r="W168" s="8"/>
     </row>
-    <row r="169" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A169" s="12"/>
       <c r="B169" s="12"/>
       <c r="C169" s="4"/>
@@ -12300,7 +12299,7 @@
       <c r="V169" s="8"/>
       <c r="W169" s="8"/>
     </row>
-    <row r="170" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A170" s="12"/>
       <c r="B170" s="12"/>
       <c r="C170" s="4"/>
@@ -12325,7 +12324,7 @@
       <c r="V170" s="8"/>
       <c r="W170" s="8"/>
     </row>
-    <row r="171" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A171" s="12"/>
       <c r="B171" s="12"/>
       <c r="C171" s="4"/>
@@ -12350,7 +12349,7 @@
       <c r="V171" s="8"/>
       <c r="W171" s="8"/>
     </row>
-    <row r="172" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A172" s="12"/>
       <c r="B172" s="12"/>
       <c r="C172" s="4"/>
@@ -12375,7 +12374,7 @@
       <c r="V172" s="8"/>
       <c r="W172" s="8"/>
     </row>
-    <row r="173" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A173" s="12"/>
       <c r="B173" s="12"/>
       <c r="C173" s="4"/>
@@ -12400,7 +12399,7 @@
       <c r="V173" s="8"/>
       <c r="W173" s="8"/>
     </row>
-    <row r="174" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A174" s="12"/>
       <c r="B174" s="12"/>
       <c r="C174" s="4"/>
@@ -12425,7 +12424,7 @@
       <c r="V174" s="8"/>
       <c r="W174" s="8"/>
     </row>
-    <row r="175" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A175" s="12"/>
       <c r="B175" s="12"/>
       <c r="C175" s="4"/>
@@ -12450,7 +12449,7 @@
       <c r="V175" s="8"/>
       <c r="W175" s="8"/>
     </row>
-    <row r="176" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A176" s="12"/>
       <c r="B176" s="12"/>
       <c r="C176" s="4"/>
@@ -12475,7 +12474,7 @@
       <c r="V176" s="8"/>
       <c r="W176" s="8"/>
     </row>
-    <row r="177" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A177" s="12"/>
       <c r="B177" s="12"/>
       <c r="C177" s="4"/>
@@ -12500,7 +12499,7 @@
       <c r="V177" s="8"/>
       <c r="W177" s="8"/>
     </row>
-    <row r="178" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A178" s="12"/>
       <c r="B178" s="12"/>
       <c r="C178" s="4"/>
@@ -12525,7 +12524,7 @@
       <c r="V178" s="8"/>
       <c r="W178" s="8"/>
     </row>
-    <row r="179" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A179" s="12"/>
       <c r="B179" s="12"/>
       <c r="C179" s="4"/>
@@ -12550,7 +12549,7 @@
       <c r="V179" s="8"/>
       <c r="W179" s="8"/>
     </row>
-    <row r="180" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A180" s="12"/>
       <c r="B180" s="12"/>
       <c r="C180" s="4"/>
@@ -12575,7 +12574,7 @@
       <c r="V180" s="8"/>
       <c r="W180" s="8"/>
     </row>
-    <row r="181" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A181" s="12"/>
       <c r="B181" s="12"/>
       <c r="C181" s="4"/>
@@ -12600,7 +12599,7 @@
       <c r="V181" s="8"/>
       <c r="W181" s="8"/>
     </row>
-    <row r="182" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A182" s="12"/>
       <c r="B182" s="12"/>
       <c r="C182" s="4"/>
@@ -12625,7 +12624,7 @@
       <c r="V182" s="8"/>
       <c r="W182" s="8"/>
     </row>
-    <row r="183" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A183" s="12"/>
       <c r="B183" s="12"/>
       <c r="C183" s="4"/>
@@ -12650,7 +12649,7 @@
       <c r="V183" s="8"/>
       <c r="W183" s="8"/>
     </row>
-    <row r="184" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A184" s="12"/>
       <c r="B184" s="12"/>
       <c r="C184" s="4"/>
@@ -12675,7 +12674,7 @@
       <c r="V184" s="8"/>
       <c r="W184" s="8"/>
     </row>
-    <row r="185" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A185" s="12"/>
       <c r="B185" s="12"/>
       <c r="C185" s="4"/>
@@ -12700,7 +12699,7 @@
       <c r="V185" s="8"/>
       <c r="W185" s="8"/>
     </row>
-    <row r="186" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A186" s="12"/>
       <c r="B186" s="12"/>
       <c r="C186" s="4"/>
@@ -12725,7 +12724,7 @@
       <c r="V186" s="8"/>
       <c r="W186" s="8"/>
     </row>
-    <row r="187" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A187" s="12"/>
       <c r="B187" s="12"/>
       <c r="C187" s="4"/>
@@ -12750,7 +12749,7 @@
       <c r="V187" s="8"/>
       <c r="W187" s="8"/>
     </row>
-    <row r="188" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A188" s="12"/>
       <c r="B188" s="12"/>
       <c r="C188" s="4"/>
@@ -12775,7 +12774,7 @@
       <c r="V188" s="8"/>
       <c r="W188" s="8"/>
     </row>
-    <row r="189" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A189" s="12"/>
       <c r="B189" s="12"/>
       <c r="C189" s="4"/>
@@ -12800,7 +12799,7 @@
       <c r="V189" s="8"/>
       <c r="W189" s="8"/>
     </row>
-    <row r="190" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A190" s="12"/>
       <c r="B190" s="12"/>
       <c r="C190" s="4"/>
@@ -12825,7 +12824,7 @@
       <c r="V190" s="8"/>
       <c r="W190" s="8"/>
     </row>
-    <row r="191" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A191" s="12"/>
       <c r="B191" s="12"/>
       <c r="C191" s="4"/>
@@ -12850,7 +12849,7 @@
       <c r="V191" s="8"/>
       <c r="W191" s="8"/>
     </row>
-    <row r="192" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A192" s="12"/>
       <c r="B192" s="12"/>
       <c r="C192" s="4"/>
@@ -12875,7 +12874,7 @@
       <c r="V192" s="8"/>
       <c r="W192" s="8"/>
     </row>
-    <row r="193" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A193" s="12"/>
       <c r="B193" s="12"/>
       <c r="C193" s="4"/>
@@ -12900,7 +12899,7 @@
       <c r="V193" s="8"/>
       <c r="W193" s="8"/>
     </row>
-    <row r="194" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A194" s="12"/>
       <c r="B194" s="12"/>
       <c r="C194" s="4"/>
@@ -12925,7 +12924,7 @@
       <c r="V194" s="8"/>
       <c r="W194" s="8"/>
     </row>
-    <row r="195" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A195" s="12"/>
       <c r="B195" s="12"/>
       <c r="C195" s="4"/>
@@ -12950,7 +12949,7 @@
       <c r="V195" s="8"/>
       <c r="W195" s="8"/>
     </row>
-    <row r="196" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A196" s="12"/>
       <c r="B196" s="12"/>
       <c r="C196" s="4"/>
@@ -12975,7 +12974,7 @@
       <c r="V196" s="8"/>
       <c r="W196" s="8"/>
     </row>
-    <row r="197" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A197" s="12"/>
       <c r="B197" s="12"/>
       <c r="C197" s="4"/>
@@ -13000,7 +12999,7 @@
       <c r="V197" s="8"/>
       <c r="W197" s="8"/>
     </row>
-    <row r="198" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A198" s="12"/>
       <c r="B198" s="12"/>
       <c r="C198" s="4"/>
@@ -13025,7 +13024,7 @@
       <c r="V198" s="8"/>
       <c r="W198" s="8"/>
     </row>
-    <row r="199" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A199" s="12"/>
       <c r="B199" s="12"/>
       <c r="C199" s="4"/>
@@ -13050,7 +13049,7 @@
       <c r="V199" s="8"/>
       <c r="W199" s="8"/>
     </row>
-    <row r="200" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A200" s="12"/>
       <c r="B200" s="12"/>
       <c r="C200" s="4"/>
@@ -13075,7 +13074,7 @@
       <c r="V200" s="8"/>
       <c r="W200" s="8"/>
     </row>
-    <row r="201" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A201" s="12"/>
       <c r="B201" s="12"/>
       <c r="C201" s="4"/>
@@ -13100,7 +13099,7 @@
       <c r="V201" s="8"/>
       <c r="W201" s="8"/>
     </row>
-    <row r="202" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A202" s="12"/>
       <c r="B202" s="12"/>
       <c r="C202" s="4"/>
@@ -13125,7 +13124,7 @@
       <c r="V202" s="8"/>
       <c r="W202" s="8"/>
     </row>
-    <row r="203" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A203" s="12"/>
       <c r="B203" s="12"/>
       <c r="C203" s="4"/>
@@ -13150,7 +13149,7 @@
       <c r="V203" s="8"/>
       <c r="W203" s="8"/>
     </row>
-    <row r="204" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A204" s="12"/>
       <c r="B204" s="12"/>
       <c r="C204" s="4"/>
@@ -13175,7 +13174,7 @@
       <c r="V204" s="8"/>
       <c r="W204" s="8"/>
     </row>
-    <row r="205" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A205" s="12"/>
       <c r="B205" s="12"/>
       <c r="C205" s="4"/>
@@ -13200,7 +13199,7 @@
       <c r="V205" s="8"/>
       <c r="W205" s="8"/>
     </row>
-    <row r="206" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A206" s="12"/>
       <c r="B206" s="12"/>
       <c r="C206" s="4"/>
@@ -13225,7 +13224,7 @@
       <c r="V206" s="8"/>
       <c r="W206" s="8"/>
     </row>
-    <row r="207" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A207" s="12"/>
       <c r="B207" s="12"/>
       <c r="C207" s="4"/>
@@ -13250,7 +13249,7 @@
       <c r="V207" s="8"/>
       <c r="W207" s="8"/>
     </row>
-    <row r="208" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A208" s="12"/>
       <c r="B208" s="12"/>
       <c r="C208" s="4"/>
@@ -13275,7 +13274,7 @@
       <c r="V208" s="8"/>
       <c r="W208" s="8"/>
     </row>
-    <row r="209" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A209" s="12"/>
       <c r="B209" s="12"/>
       <c r="C209" s="4"/>
@@ -13300,7 +13299,7 @@
       <c r="V209" s="8"/>
       <c r="W209" s="8"/>
     </row>
-    <row r="210" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A210" s="12"/>
       <c r="B210" s="12"/>
       <c r="C210" s="4"/>
@@ -13325,7 +13324,7 @@
       <c r="V210" s="8"/>
       <c r="W210" s="8"/>
     </row>
-    <row r="211" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A211" s="12"/>
       <c r="B211" s="12"/>
       <c r="C211" s="4"/>
@@ -13350,7 +13349,7 @@
       <c r="V211" s="8"/>
       <c r="W211" s="8"/>
     </row>
-    <row r="212" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A212" s="12"/>
       <c r="B212" s="12"/>
       <c r="C212" s="4"/>
@@ -13375,7 +13374,7 @@
       <c r="V212" s="8"/>
       <c r="W212" s="8"/>
     </row>
-    <row r="213" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A213" s="12"/>
       <c r="B213" s="12"/>
       <c r="C213" s="4"/>
@@ -13400,7 +13399,7 @@
       <c r="V213" s="8"/>
       <c r="W213" s="8"/>
     </row>
-    <row r="214" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A214" s="12"/>
       <c r="B214" s="12"/>
       <c r="C214" s="4"/>
@@ -13425,7 +13424,7 @@
       <c r="V214" s="8"/>
       <c r="W214" s="8"/>
     </row>
-    <row r="215" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A215" s="12"/>
       <c r="B215" s="12"/>
       <c r="C215" s="4"/>
@@ -13450,7 +13449,7 @@
       <c r="V215" s="8"/>
       <c r="W215" s="8"/>
     </row>
-    <row r="216" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A216" s="12"/>
       <c r="B216" s="12"/>
       <c r="C216" s="4"/>
@@ -13475,7 +13474,7 @@
       <c r="V216" s="8"/>
       <c r="W216" s="8"/>
     </row>
-    <row r="217" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A217" s="12"/>
       <c r="B217" s="12"/>
       <c r="C217" s="4"/>
@@ -13500,7 +13499,7 @@
       <c r="V217" s="8"/>
       <c r="W217" s="8"/>
     </row>
-    <row r="218" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A218" s="12"/>
       <c r="B218" s="12"/>
       <c r="C218" s="4"/>
@@ -13525,7 +13524,7 @@
       <c r="V218" s="8"/>
       <c r="W218" s="8"/>
     </row>
-    <row r="219" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A219" s="12"/>
       <c r="B219" s="12"/>
       <c r="C219" s="4"/>
@@ -13550,7 +13549,7 @@
       <c r="V219" s="8"/>
       <c r="W219" s="8"/>
     </row>
-    <row r="220" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A220" s="12"/>
       <c r="B220" s="12"/>
       <c r="C220" s="4"/>
@@ -13575,7 +13574,7 @@
       <c r="V220" s="8"/>
       <c r="W220" s="8"/>
     </row>
-    <row r="221" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A221" s="12"/>
       <c r="B221" s="12"/>
       <c r="C221" s="4"/>
@@ -13600,7 +13599,7 @@
       <c r="V221" s="8"/>
       <c r="W221" s="8"/>
     </row>
-    <row r="222" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A222" s="12"/>
       <c r="B222" s="12"/>
       <c r="C222" s="4"/>
@@ -13625,7 +13624,7 @@
       <c r="V222" s="8"/>
       <c r="W222" s="8"/>
     </row>
-    <row r="223" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A223" s="12"/>
       <c r="B223" s="12"/>
       <c r="C223" s="4"/>
@@ -13650,7 +13649,7 @@
       <c r="V223" s="8"/>
       <c r="W223" s="8"/>
     </row>
-    <row r="224" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A224" s="12"/>
       <c r="B224" s="12"/>
       <c r="C224" s="4"/>
@@ -13675,7 +13674,7 @@
       <c r="V224" s="8"/>
       <c r="W224" s="8"/>
     </row>
-    <row r="225" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A225" s="12"/>
       <c r="B225" s="12"/>
       <c r="C225" s="4"/>
@@ -13700,7 +13699,7 @@
       <c r="V225" s="8"/>
       <c r="W225" s="8"/>
     </row>
-    <row r="226" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A226" s="12"/>
       <c r="B226" s="12"/>
       <c r="C226" s="4"/>
@@ -13725,7 +13724,7 @@
       <c r="V226" s="8"/>
       <c r="W226" s="8"/>
     </row>
-    <row r="227" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A227" s="12"/>
       <c r="B227" s="12"/>
       <c r="C227" s="4"/>
@@ -13750,7 +13749,7 @@
       <c r="V227" s="8"/>
       <c r="W227" s="8"/>
     </row>
-    <row r="228" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A228" s="12"/>
       <c r="B228" s="12"/>
       <c r="C228" s="4"/>
@@ -13775,7 +13774,7 @@
       <c r="V228" s="8"/>
       <c r="W228" s="8"/>
     </row>
-    <row r="229" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A229" s="12"/>
       <c r="B229" s="12"/>
       <c r="C229" s="4"/>
@@ -13800,7 +13799,7 @@
       <c r="V229" s="8"/>
       <c r="W229" s="8"/>
     </row>
-    <row r="230" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A230" s="12"/>
       <c r="B230" s="12"/>
       <c r="C230" s="4"/>
@@ -13825,7 +13824,7 @@
       <c r="V230" s="8"/>
       <c r="W230" s="8"/>
     </row>
-    <row r="231" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A231" s="12"/>
       <c r="B231" s="12"/>
       <c r="C231" s="4"/>
@@ -13850,7 +13849,7 @@
       <c r="V231" s="8"/>
       <c r="W231" s="8"/>
     </row>
-    <row r="232" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A232" s="12"/>
       <c r="B232" s="12"/>
       <c r="C232" s="4"/>
@@ -13875,7 +13874,7 @@
       <c r="V232" s="8"/>
       <c r="W232" s="8"/>
     </row>
-    <row r="233" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A233" s="12"/>
       <c r="B233" s="12"/>
       <c r="C233" s="4"/>
@@ -13900,7 +13899,7 @@
       <c r="V233" s="8"/>
       <c r="W233" s="8"/>
     </row>
-    <row r="234" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A234" s="12"/>
       <c r="B234" s="12"/>
       <c r="C234" s="4"/>
@@ -13925,7 +13924,7 @@
       <c r="V234" s="8"/>
       <c r="W234" s="8"/>
     </row>
-    <row r="235" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A235" s="12"/>
       <c r="B235" s="12"/>
       <c r="C235" s="4"/>
@@ -13950,7 +13949,7 @@
       <c r="V235" s="8"/>
       <c r="W235" s="8"/>
     </row>
-    <row r="236" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A236" s="12"/>
       <c r="B236" s="12"/>
       <c r="C236" s="4"/>
@@ -13975,7 +13974,7 @@
       <c r="V236" s="8"/>
       <c r="W236" s="8"/>
     </row>
-    <row r="237" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A237" s="12"/>
       <c r="B237" s="12"/>
       <c r="C237" s="4"/>
@@ -14000,7 +13999,7 @@
       <c r="V237" s="8"/>
       <c r="W237" s="8"/>
     </row>
-    <row r="238" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A238" s="12"/>
       <c r="B238" s="12"/>
       <c r="C238" s="4"/>
@@ -14025,7 +14024,7 @@
       <c r="V238" s="8"/>
       <c r="W238" s="8"/>
     </row>
-    <row r="239" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A239" s="12"/>
       <c r="B239" s="12"/>
       <c r="C239" s="4"/>
@@ -14050,7 +14049,7 @@
       <c r="V239" s="8"/>
       <c r="W239" s="8"/>
     </row>
-    <row r="240" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A240" s="12"/>
       <c r="B240" s="12"/>
       <c r="C240" s="4"/>
@@ -14075,7 +14074,7 @@
       <c r="V240" s="8"/>
       <c r="W240" s="8"/>
     </row>
-    <row r="241" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A241" s="12"/>
       <c r="B241" s="12"/>
       <c r="C241" s="4"/>
@@ -14100,7 +14099,7 @@
       <c r="V241" s="8"/>
       <c r="W241" s="8"/>
     </row>
-    <row r="242" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A242" s="12"/>
       <c r="B242" s="12"/>
       <c r="C242" s="4"/>
@@ -14125,7 +14124,7 @@
       <c r="V242" s="8"/>
       <c r="W242" s="8"/>
     </row>
-    <row r="243" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A243" s="12"/>
       <c r="B243" s="12"/>
       <c r="C243" s="4"/>
@@ -14150,7 +14149,7 @@
       <c r="V243" s="8"/>
       <c r="W243" s="8"/>
     </row>
-    <row r="244" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A244" s="12"/>
       <c r="B244" s="12"/>
       <c r="C244" s="4"/>
@@ -14175,7 +14174,7 @@
       <c r="V244" s="8"/>
       <c r="W244" s="8"/>
     </row>
-    <row r="245" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A245" s="12"/>
       <c r="B245" s="12"/>
       <c r="C245" s="4"/>
@@ -14200,7 +14199,7 @@
       <c r="V245" s="8"/>
       <c r="W245" s="8"/>
     </row>
-    <row r="246" spans="1:23" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" ht="20.25" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A246" s="12"/>
       <c r="B246" s="12"/>
       <c r="C246" s="4"/>
@@ -14225,7 +14224,7 @@
       <c r="V246" s="8"/>
       <c r="W246" s="8"/>
     </row>
-    <row r="247" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A247" s="12"/>
       <c r="B247" s="12"/>
       <c r="C247" s="4"/>
@@ -14250,7 +14249,7 @@
       <c r="V247" s="8"/>
       <c r="W247" s="8"/>
     </row>
-    <row r="248" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A248" s="12"/>
       <c r="B248" s="12"/>
       <c r="C248" s="4"/>
@@ -14275,7 +14274,7 @@
       <c r="V248" s="8"/>
       <c r="W248" s="8"/>
     </row>
-    <row r="249" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A249" s="12"/>
       <c r="B249" s="12"/>
       <c r="C249" s="4"/>
@@ -14300,7 +14299,7 @@
       <c r="V249" s="8"/>
       <c r="W249" s="8"/>
     </row>
-    <row r="250" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A250" s="12"/>
       <c r="B250" s="12"/>
       <c r="C250" s="4"/>
@@ -14325,7 +14324,7 @@
       <c r="V250" s="8"/>
       <c r="W250" s="8"/>
     </row>
-    <row r="251" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A251" s="12"/>
       <c r="B251" s="12"/>
       <c r="C251" s="4"/>
@@ -14350,7 +14349,7 @@
       <c r="V251" s="8"/>
       <c r="W251" s="8"/>
     </row>
-    <row r="252" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A252" s="12"/>
       <c r="B252" s="12"/>
       <c r="C252" s="4"/>
@@ -14375,7 +14374,7 @@
       <c r="V252" s="8"/>
       <c r="W252" s="8"/>
     </row>
-    <row r="253" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A253" s="12"/>
       <c r="B253" s="12"/>
       <c r="C253" s="4"/>
@@ -14400,7 +14399,7 @@
       <c r="V253" s="8"/>
       <c r="W253" s="8"/>
     </row>
-    <row r="254" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A254" s="12"/>
       <c r="B254" s="12"/>
       <c r="C254" s="4"/>
@@ -14425,7 +14424,7 @@
       <c r="V254" s="8"/>
       <c r="W254" s="8"/>
     </row>
-    <row r="255" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A255" s="12"/>
       <c r="B255" s="12"/>
       <c r="C255" s="4"/>
@@ -14450,7 +14449,7 @@
       <c r="V255" s="8"/>
       <c r="W255" s="8"/>
     </row>
-    <row r="256" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A256" s="12"/>
       <c r="B256" s="12"/>
       <c r="C256" s="4"/>
@@ -14475,7 +14474,7 @@
       <c r="V256" s="8"/>
       <c r="W256" s="8"/>
     </row>
-    <row r="257" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A257" s="12"/>
       <c r="B257" s="12"/>
       <c r="C257" s="4"/>
@@ -14500,7 +14499,7 @@
       <c r="V257" s="8"/>
       <c r="W257" s="8"/>
     </row>
-    <row r="258" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A258" s="12"/>
       <c r="B258" s="12"/>
       <c r="C258" s="4"/>
@@ -14525,7 +14524,7 @@
       <c r="V258" s="8"/>
       <c r="W258" s="8"/>
     </row>
-    <row r="259" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A259" s="12"/>
       <c r="B259" s="12"/>
       <c r="C259" s="4"/>
@@ -14550,7 +14549,7 @@
       <c r="V259" s="8"/>
       <c r="W259" s="8"/>
     </row>
-    <row r="260" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A260" s="12"/>
       <c r="B260" s="12"/>
       <c r="C260" s="4"/>
@@ -14575,7 +14574,7 @@
       <c r="V260" s="8"/>
       <c r="W260" s="8"/>
     </row>
-    <row r="261" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A261" s="12"/>
       <c r="B261" s="12"/>
       <c r="C261" s="4"/>
@@ -14600,7 +14599,7 @@
       <c r="V261" s="8"/>
       <c r="W261" s="8"/>
     </row>
-    <row r="262" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A262" s="12"/>
       <c r="B262" s="12"/>
       <c r="C262" s="4"/>
@@ -14625,7 +14624,7 @@
       <c r="V262" s="8"/>
       <c r="W262" s="8"/>
     </row>
-    <row r="263" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A263" s="12"/>
       <c r="B263" s="12"/>
       <c r="C263" s="4"/>
@@ -14650,7 +14649,7 @@
       <c r="V263" s="8"/>
       <c r="W263" s="8"/>
     </row>
-    <row r="264" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A264" s="12"/>
       <c r="B264" s="12"/>
       <c r="C264" s="4"/>
@@ -14675,7 +14674,7 @@
       <c r="V264" s="8"/>
       <c r="W264" s="8"/>
     </row>
-    <row r="265" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A265" s="12"/>
       <c r="B265" s="12"/>
       <c r="C265" s="4"/>
@@ -14700,7 +14699,7 @@
       <c r="V265" s="8"/>
       <c r="W265" s="8"/>
     </row>
-    <row r="266" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A266" s="12"/>
       <c r="B266" s="12"/>
       <c r="C266" s="4"/>
@@ -14725,7 +14724,7 @@
       <c r="V266" s="8"/>
       <c r="W266" s="8"/>
     </row>
-    <row r="267" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A267" s="12"/>
       <c r="B267" s="12"/>
       <c r="C267" s="4"/>
@@ -14750,7 +14749,7 @@
       <c r="V267" s="8"/>
       <c r="W267" s="8"/>
     </row>
-    <row r="268" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A268" s="12"/>
       <c r="B268" s="12"/>
       <c r="C268" s="4"/>
@@ -14775,7 +14774,7 @@
       <c r="V268" s="8"/>
       <c r="W268" s="8"/>
     </row>
-    <row r="269" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" ht="21" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A269" s="12"/>
       <c r="B269" s="12"/>
       <c r="C269" s="4"/>
@@ -14806,14 +14805,14 @@
     <mergeCell ref="I11:J11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.140625" customWidth="1"/>
     <col min="2" max="2" width="20.42578125" customWidth="1"/>
@@ -14824,7 +14823,7 @@
       <c r="A1" t="s">
         <v>119</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="20" t="s">
         <v>120</v>
       </c>
     </row>
@@ -14842,17 +14841,17 @@
         <v>123</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>125</v>
       </c>
@@ -14865,12 +14864,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>62</v>
       </c>
@@ -14880,6 +14879,6 @@
     <mergeCell ref="A2:B2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/new_sales_order_sheet_format 1 - Copy-1 (6).xlsx
+++ b/new_sales_order_sheet_format 1 - Copy-1 (6).xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="15720" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet sheetId="1" name="Previous" state="visible" r:id="rId4"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="127">
   <si>
     <t>xf_date</t>
   </si>
@@ -318,10 +318,7 @@
     <t>Sep.14,2026</t>
   </si>
   <si>
-    <t>CAT784-1A23S</t>
-  </si>
-  <si>
-    <t>15E09A9153</t>
+    <t>15E09A9176</t>
   </si>
   <si>
     <t>Dec.12,2025</t>
@@ -330,43 +327,43 @@
     <t>AW2026</t>
   </si>
   <si>
-    <t>CAT000-1A029</t>
+    <t>CAT000-1A052</t>
   </si>
   <si>
-    <t>15F09A9153</t>
+    <t>15F09A9176</t>
   </si>
   <si>
     <t>CAT960-1A23S</t>
   </si>
   <si>
-    <t>15G09A9153</t>
+    <t>15G09A9176</t>
   </si>
   <si>
-    <t>15H09A9153</t>
+    <t>15H09A9176</t>
   </si>
   <si>
-    <t>15I09A9153</t>
+    <t>15I09A9176</t>
   </si>
   <si>
     <t>CAT888-1A23S</t>
   </si>
   <si>
-    <t>15J09A9153</t>
+    <t>15J09A9176</t>
   </si>
   <si>
     <t>CAT1100-1A23W</t>
   </si>
   <si>
-    <t>15K09A9153</t>
+    <t>15K09A9176</t>
   </si>
   <si>
     <t>CAT1100-3A23W</t>
   </si>
   <si>
-    <t>15L09A9153</t>
+    <t>15L09A9176</t>
   </si>
   <si>
-    <t>15M09A9153</t>
+    <t>15M09A9176</t>
   </si>
   <si>
     <t>Olny Excel formate Change</t>
@@ -7528,7 +7525,7 @@
         <v>24</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>100</v>
+        <v>26</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>27</v>
@@ -7541,7 +7538,7 @@
       </c>
       <c r="J2" s="5"/>
       <c r="K2" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L2" s="6" t="s">
         <v>30</v>
@@ -7555,7 +7552,7 @@
         <v>32</v>
       </c>
       <c r="Q2" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="R2" s="7" t="s">
         <v>34</v>
@@ -7573,7 +7570,7 @@
         <v>3190427</v>
       </c>
       <c r="W2" s="16" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="X2" s="4"/>
       <c r="Y2" s="6"/>
@@ -7602,7 +7599,7 @@
         <v>24</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>41</v>
@@ -7615,7 +7612,7 @@
       </c>
       <c r="J3" s="5"/>
       <c r="K3" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L3" s="6" t="s">
         <v>30</v>
@@ -7629,7 +7626,7 @@
         <v>32</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="R3" s="7" t="s">
         <v>43</v>
@@ -7647,7 +7644,7 @@
         <v>3190428</v>
       </c>
       <c r="W3" s="16" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="X3" s="4"/>
       <c r="Y3" s="6"/>
@@ -7676,7 +7673,7 @@
         <v>24</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>48</v>
@@ -7689,7 +7686,7 @@
       </c>
       <c r="J4" s="5"/>
       <c r="K4" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L4" s="6" t="s">
         <v>30</v>
@@ -7703,7 +7700,7 @@
         <v>32</v>
       </c>
       <c r="Q4" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="R4" s="7" t="s">
         <v>50</v>
@@ -7721,7 +7718,7 @@
         <v>3190429</v>
       </c>
       <c r="W4" s="16" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="X4" s="4"/>
       <c r="Y4" s="6"/>
@@ -7763,7 +7760,7 @@
       </c>
       <c r="J5" s="5"/>
       <c r="K5" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L5" s="6" t="s">
         <v>58</v>
@@ -7777,7 +7774,7 @@
         <v>32</v>
       </c>
       <c r="Q5" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="R5" s="7" t="s">
         <v>60</v>
@@ -7795,7 +7792,7 @@
         <v>3190249</v>
       </c>
       <c r="W5" s="16" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="X5" s="4"/>
       <c r="Y5" s="6"/>
@@ -7837,7 +7834,7 @@
       </c>
       <c r="J6" s="5"/>
       <c r="K6" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L6" s="6" t="s">
         <v>58</v>
@@ -7851,7 +7848,7 @@
         <v>32</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="R6" s="7" t="s">
         <v>60</v>
@@ -7869,7 +7866,7 @@
         <v>3190250</v>
       </c>
       <c r="W6" s="16" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="X6" s="4"/>
       <c r="Y6" s="6"/>
@@ -7898,7 +7895,7 @@
         <v>24</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>70</v>
@@ -7911,7 +7908,7 @@
       </c>
       <c r="J7" s="5"/>
       <c r="K7" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L7" s="6" t="s">
         <v>58</v>
@@ -7925,7 +7922,7 @@
         <v>32</v>
       </c>
       <c r="Q7" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="R7" s="7" t="s">
         <v>72</v>
@@ -7943,7 +7940,7 @@
         <v>3190251</v>
       </c>
       <c r="W7" s="16" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="X7" s="4"/>
       <c r="Y7" s="6"/>
@@ -7972,7 +7969,7 @@
         <v>24</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>78</v>
@@ -7985,7 +7982,7 @@
       </c>
       <c r="J8" s="5"/>
       <c r="K8" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>80</v>
@@ -7999,7 +7996,7 @@
         <v>32</v>
       </c>
       <c r="Q8" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="R8" s="7" t="s">
         <v>82</v>
@@ -8017,7 +8014,7 @@
         <v>3190608</v>
       </c>
       <c r="W8" s="16" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="X8" s="4"/>
       <c r="Y8" s="6"/>
@@ -8046,7 +8043,7 @@
         <v>24</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>88</v>
@@ -8059,7 +8056,7 @@
       </c>
       <c r="J9" s="5"/>
       <c r="K9" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L9" s="6" t="s">
         <v>80</v>
@@ -8073,7 +8070,7 @@
         <v>32</v>
       </c>
       <c r="Q9" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="R9" s="7" t="s">
         <v>90</v>
@@ -8091,7 +8088,7 @@
         <v>3190609</v>
       </c>
       <c r="W9" s="16" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="X9" s="4"/>
       <c r="Y9" s="6"/>
@@ -8120,7 +8117,7 @@
         <v>24</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>88</v>
@@ -8133,7 +8130,7 @@
       </c>
       <c r="J10" s="5"/>
       <c r="K10" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L10" s="6" t="s">
         <v>80</v>
@@ -8147,7 +8144,7 @@
         <v>32</v>
       </c>
       <c r="Q10" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="R10" s="7" t="s">
         <v>90</v>
@@ -8165,7 +8162,7 @@
         <v>3190609</v>
       </c>
       <c r="W10" s="16" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="X10" s="4"/>
       <c r="Y10" s="6"/>
@@ -8179,7 +8176,7 @@
     </row>
     <row r="11" ht="21" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B11" s="17"/>
       <c r="C11" s="4" t="s">
@@ -8191,7 +8188,7 @@
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
       <c r="I11" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J11" s="17"/>
       <c r="K11" s="4"/>
@@ -8201,7 +8198,7 @@
       <c r="O11" s="6"/>
       <c r="P11" s="6"/>
       <c r="Q11" s="18" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="R11" s="7"/>
       <c r="S11" s="4"/>
@@ -8209,7 +8206,7 @@
       <c r="U11" s="8"/>
       <c r="V11" s="8"/>
       <c r="W11" s="19" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="X11" s="6"/>
       <c r="Y11" s="6"/>
@@ -14821,24 +14818,24 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B1" s="20" t="s">
         <v>119</v>
-      </c>
-      <c r="B1" s="20" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="21" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B2" s="21"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>121</v>
+      </c>
+      <c r="B5" t="s">
         <v>122</v>
-      </c>
-      <c r="B5" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="6" spans="2:2" x14ac:dyDescent="0.25">
@@ -14848,17 +14845,17 @@
     </row>
     <row r="7" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B11" t="s">
         <v>36</v>
@@ -14866,7 +14863,7 @@
     </row>
     <row r="12" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13" spans="2:2" x14ac:dyDescent="0.25">
